--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -2209,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839390</v>
+        <v>119839386</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>100080</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,42 +2221,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>222771</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519992</v>
+        <v>520045</v>
       </c>
       <c r="R17" t="n">
-        <v>6967862</v>
+        <v>6967714</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2291,17 +2287,13 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>varav 1 hane, den andra såg jag inte . Båda trummade</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2320,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119839386</v>
+        <v>119839390</v>
       </c>
       <c r="B18" t="n">
-        <v>100080</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,38 +2324,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222771</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520045</v>
+        <v>519992</v>
       </c>
       <c r="R18" t="n">
-        <v>6967714</v>
+        <v>6967862</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2398,13 +2394,17 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>varav 1 hane, den andra såg jag inte . Båda trummade</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839404</v>
+        <v>119839580</v>
       </c>
       <c r="B2" t="n">
         <v>100171</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520154</v>
+        <v>520045</v>
       </c>
       <c r="R2" t="n">
-        <v>6967747</v>
+        <v>6967714</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839397</v>
+        <v>119839566</v>
       </c>
       <c r="B3" t="n">
-        <v>100080</v>
+        <v>103418</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520153</v>
+        <v>520227</v>
       </c>
       <c r="R3" t="n">
-        <v>6967764</v>
+        <v>6967737</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,7 +861,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119839572</v>
+        <v>119839399</v>
       </c>
       <c r="B4" t="n">
-        <v>102825</v>
+        <v>91494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222002</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520020</v>
+        <v>520154</v>
       </c>
       <c r="R4" t="n">
-        <v>6967619</v>
+        <v>6967747</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -982,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119839574</v>
+        <v>119839573</v>
       </c>
       <c r="B5" t="n">
-        <v>100080</v>
+        <v>101074</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1022,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520106</v>
+        <v>520045</v>
       </c>
       <c r="R5" t="n">
-        <v>6967615</v>
+        <v>6967588</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1065,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1085,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119839399</v>
+        <v>119839574</v>
       </c>
       <c r="B6" t="n">
-        <v>91494</v>
+        <v>100080</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1101,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1125,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520154</v>
+        <v>520106</v>
       </c>
       <c r="R6" t="n">
-        <v>6967747</v>
+        <v>6967615</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1169,6 +1167,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1187,7 +1186,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119839579</v>
+        <v>119839386</v>
       </c>
       <c r="B7" t="n">
         <v>100080</v>
@@ -1227,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520067</v>
+        <v>520045</v>
       </c>
       <c r="R7" t="n">
-        <v>6967702</v>
+        <v>6967714</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1290,7 +1289,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119839580</v>
+        <v>119839571</v>
       </c>
       <c r="B8" t="n">
         <v>100171</v>
@@ -1330,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520045</v>
+        <v>520020</v>
       </c>
       <c r="R8" t="n">
-        <v>6967714</v>
+        <v>6967619</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1392,10 +1391,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119839403</v>
+        <v>119839572</v>
       </c>
       <c r="B9" t="n">
-        <v>101074</v>
+        <v>102825</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1408,21 +1407,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>222002</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1432,10 +1431,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520154</v>
+        <v>520020</v>
       </c>
       <c r="R9" t="n">
-        <v>6967747</v>
+        <v>6967619</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1494,10 +1493,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119839385</v>
+        <v>119839563</v>
       </c>
       <c r="B10" t="n">
-        <v>103418</v>
+        <v>100080</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1510,16 +1509,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1534,10 +1533,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520045</v>
+        <v>520185</v>
       </c>
       <c r="R10" t="n">
-        <v>6967714</v>
+        <v>6967760</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1578,6 +1577,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1596,7 +1596,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119839563</v>
+        <v>119839397</v>
       </c>
       <c r="B11" t="n">
         <v>100080</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520185</v>
+        <v>520153</v>
       </c>
       <c r="R11" t="n">
-        <v>6967760</v>
+        <v>6967764</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119839570</v>
+        <v>119839385</v>
       </c>
       <c r="B12" t="n">
-        <v>101074</v>
+        <v>103418</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520020</v>
+        <v>520045</v>
       </c>
       <c r="R12" t="n">
-        <v>6967619</v>
+        <v>6967714</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1801,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119839577</v>
+        <v>119839396</v>
       </c>
       <c r="B13" t="n">
-        <v>90562</v>
+        <v>103418</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,25 +1813,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>222412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520121</v>
+        <v>520139</v>
       </c>
       <c r="R13" t="n">
-        <v>6967669</v>
+        <v>6967793</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839398</v>
+        <v>119839570</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>101074</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,25 +1915,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221235</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520154</v>
+        <v>520020</v>
       </c>
       <c r="R14" t="n">
-        <v>6967747</v>
+        <v>6967619</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839573</v>
+        <v>119839398</v>
       </c>
       <c r="B15" t="n">
-        <v>101074</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,25 +2017,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520045</v>
+        <v>520154</v>
       </c>
       <c r="R15" t="n">
-        <v>6967588</v>
+        <v>6967747</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119839396</v>
+        <v>119839569</v>
       </c>
       <c r="B16" t="n">
-        <v>103418</v>
+        <v>79607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,25 +2119,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520139</v>
+        <v>520132</v>
       </c>
       <c r="R16" t="n">
-        <v>6967793</v>
+        <v>6967651</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2185,12 +2185,18 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>på asp</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2209,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839386</v>
+        <v>119839390</v>
       </c>
       <c r="B17" t="n">
-        <v>100080</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,38 +2227,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222771</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520045</v>
+        <v>519992</v>
       </c>
       <c r="R17" t="n">
-        <v>6967714</v>
+        <v>6967862</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2287,13 +2297,17 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>varav 1 hane, den andra såg jag inte . Båda trummade</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2312,10 +2326,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119839390</v>
+        <v>119839577</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,38 +2342,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519992</v>
+        <v>520121</v>
       </c>
       <c r="R18" t="n">
-        <v>6967862</v>
+        <v>6967669</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2392,11 +2402,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>varav 1 hane, den andra såg jag inte . Båda trummade</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2423,7 +2428,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839571</v>
+        <v>119839404</v>
       </c>
       <c r="B19" t="n">
         <v>100171</v>
@@ -2463,10 +2468,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520020</v>
+        <v>520154</v>
       </c>
       <c r="R19" t="n">
-        <v>6967619</v>
+        <v>6967747</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2525,10 +2530,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839566</v>
+        <v>119839579</v>
       </c>
       <c r="B20" t="n">
-        <v>103418</v>
+        <v>100080</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2541,16 +2546,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2565,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520227</v>
+        <v>520067</v>
       </c>
       <c r="R20" t="n">
-        <v>6967737</v>
+        <v>6967702</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2609,6 +2614,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2627,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119839569</v>
+        <v>119839403</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>101074</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,25 +2645,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2667,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520132</v>
+        <v>520154</v>
       </c>
       <c r="R21" t="n">
-        <v>6967651</v>
+        <v>6967747</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2705,18 +2711,12 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>på asp</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -2107,10 +2107,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119839569</v>
+        <v>119839390</v>
       </c>
       <c r="B16" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2123,34 +2123,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520132</v>
+        <v>519992</v>
       </c>
       <c r="R16" t="n">
-        <v>6967651</v>
+        <v>6967862</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2187,7 +2191,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>på asp</t>
+          <t>varav 1 hane, den andra såg jag inte . Båda trummade</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2196,7 +2200,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2215,10 +2218,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839390</v>
+        <v>119839569</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,38 +2234,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519992</v>
+        <v>520132</v>
       </c>
       <c r="R17" t="n">
-        <v>6967862</v>
+        <v>6967651</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2299,7 +2298,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>varav 1 hane, den andra såg jag inte . Båda trummade</t>
+          <t>på asp</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2308,6 +2307,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839580</v>
+        <v>119839569</v>
       </c>
       <c r="B2" t="n">
-        <v>100171</v>
+        <v>79607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520045</v>
+        <v>520132</v>
       </c>
       <c r="R2" t="n">
-        <v>6967714</v>
+        <v>6967651</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,12 +753,18 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>på asp</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839566</v>
+        <v>119839404</v>
       </c>
       <c r="B3" t="n">
-        <v>103418</v>
+        <v>100171</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +799,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520227</v>
+        <v>520154</v>
       </c>
       <c r="R3" t="n">
-        <v>6967737</v>
+        <v>6967747</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119839399</v>
+        <v>119839566</v>
       </c>
       <c r="B4" t="n">
-        <v>91494</v>
+        <v>103418</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +901,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520154</v>
+        <v>520227</v>
       </c>
       <c r="R4" t="n">
-        <v>6967747</v>
+        <v>6967737</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,7 +987,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119839573</v>
+        <v>119839403</v>
       </c>
       <c r="B5" t="n">
         <v>101074</v>
@@ -1021,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520045</v>
+        <v>520154</v>
       </c>
       <c r="R5" t="n">
-        <v>6967588</v>
+        <v>6967747</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119839574</v>
+        <v>119839573</v>
       </c>
       <c r="B6" t="n">
-        <v>100080</v>
+        <v>101074</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1105,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520106</v>
+        <v>520045</v>
       </c>
       <c r="R6" t="n">
-        <v>6967615</v>
+        <v>6967588</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1167,7 +1173,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1186,7 +1191,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119839386</v>
+        <v>119839397</v>
       </c>
       <c r="B7" t="n">
         <v>100080</v>
@@ -1226,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520045</v>
+        <v>520153</v>
       </c>
       <c r="R7" t="n">
-        <v>6967714</v>
+        <v>6967764</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1289,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119839571</v>
+        <v>119839399</v>
       </c>
       <c r="B8" t="n">
-        <v>100171</v>
+        <v>91494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1305,21 +1310,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1329,10 +1334,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520020</v>
+        <v>520154</v>
       </c>
       <c r="R8" t="n">
-        <v>6967619</v>
+        <v>6967747</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1391,10 +1396,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119839572</v>
+        <v>119839398</v>
       </c>
       <c r="B9" t="n">
-        <v>102825</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1403,25 +1408,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222002</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1431,10 +1436,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520020</v>
+        <v>520154</v>
       </c>
       <c r="R9" t="n">
-        <v>6967619</v>
+        <v>6967747</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1493,10 +1498,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119839563</v>
+        <v>119839577</v>
       </c>
       <c r="B10" t="n">
-        <v>100080</v>
+        <v>90562</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1505,25 +1510,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1533,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520185</v>
+        <v>520121</v>
       </c>
       <c r="R10" t="n">
-        <v>6967760</v>
+        <v>6967669</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1577,7 +1582,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1596,7 +1600,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119839397</v>
+        <v>119839563</v>
       </c>
       <c r="B11" t="n">
         <v>100080</v>
@@ -1636,10 +1640,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520153</v>
+        <v>520185</v>
       </c>
       <c r="R11" t="n">
-        <v>6967764</v>
+        <v>6967760</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1699,10 +1703,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119839385</v>
+        <v>119839579</v>
       </c>
       <c r="B12" t="n">
-        <v>103418</v>
+        <v>100080</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1715,16 +1719,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1739,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520045</v>
+        <v>520067</v>
       </c>
       <c r="R12" t="n">
-        <v>6967714</v>
+        <v>6967702</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1783,6 +1787,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1903,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839570</v>
+        <v>119839580</v>
       </c>
       <c r="B14" t="n">
-        <v>101074</v>
+        <v>100171</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1919,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520020</v>
+        <v>520045</v>
       </c>
       <c r="R14" t="n">
-        <v>6967619</v>
+        <v>6967714</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2005,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839398</v>
+        <v>119839385</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>103418</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,25 +2022,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520154</v>
+        <v>520045</v>
       </c>
       <c r="R15" t="n">
-        <v>6967747</v>
+        <v>6967714</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2107,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119839390</v>
+        <v>119839572</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>102825</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,42 +2124,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>222002</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519992</v>
+        <v>520020</v>
       </c>
       <c r="R16" t="n">
-        <v>6967862</v>
+        <v>6967619</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2187,11 +2188,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>varav 1 hane, den andra såg jag inte . Båda trummade</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2218,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839569</v>
+        <v>119839571</v>
       </c>
       <c r="B17" t="n">
-        <v>79607</v>
+        <v>100171</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,25 +2226,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2258,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520132</v>
+        <v>520020</v>
       </c>
       <c r="R17" t="n">
-        <v>6967651</v>
+        <v>6967619</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2296,18 +2292,12 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>på asp</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2326,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119839577</v>
+        <v>119839574</v>
       </c>
       <c r="B18" t="n">
-        <v>90562</v>
+        <v>100080</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,25 +2328,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2366,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520121</v>
+        <v>520106</v>
       </c>
       <c r="R18" t="n">
-        <v>6967669</v>
+        <v>6967615</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2410,6 +2400,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2428,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839404</v>
+        <v>119839390</v>
       </c>
       <c r="B19" t="n">
-        <v>100171</v>
+        <v>57310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,38 +2431,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520154</v>
+        <v>519992</v>
       </c>
       <c r="R19" t="n">
-        <v>6967747</v>
+        <v>6967862</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2504,6 +2499,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>varav 1 hane, den andra såg jag inte . Båda trummade</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2530,7 +2530,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839579</v>
+        <v>119839386</v>
       </c>
       <c r="B20" t="n">
         <v>100080</v>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520067</v>
+        <v>520045</v>
       </c>
       <c r="R20" t="n">
-        <v>6967702</v>
+        <v>6967714</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2633,7 +2633,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119839403</v>
+        <v>119839570</v>
       </c>
       <c r="B21" t="n">
         <v>101074</v>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520154</v>
+        <v>520020</v>
       </c>
       <c r="R21" t="n">
-        <v>6967747</v>
+        <v>6967619</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839569</v>
+        <v>119839403</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
+        <v>101074</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520132</v>
+        <v>520154</v>
       </c>
       <c r="R2" t="n">
-        <v>6967651</v>
+        <v>6967747</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,18 +753,12 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>på asp</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839404</v>
+        <v>119839563</v>
       </c>
       <c r="B3" t="n">
-        <v>100171</v>
+        <v>100080</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520154</v>
+        <v>520185</v>
       </c>
       <c r="R3" t="n">
-        <v>6967747</v>
+        <v>6967760</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,6 +861,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -885,10 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119839566</v>
+        <v>119839570</v>
       </c>
       <c r="B4" t="n">
-        <v>103418</v>
+        <v>101074</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520227</v>
+        <v>520020</v>
       </c>
       <c r="R4" t="n">
-        <v>6967737</v>
+        <v>6967619</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -987,7 +982,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119839403</v>
+        <v>119839573</v>
       </c>
       <c r="B5" t="n">
         <v>101074</v>
@@ -1027,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520154</v>
+        <v>520045</v>
       </c>
       <c r="R5" t="n">
-        <v>6967747</v>
+        <v>6967588</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1089,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119839573</v>
+        <v>119839574</v>
       </c>
       <c r="B6" t="n">
-        <v>101074</v>
+        <v>100080</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1129,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520045</v>
+        <v>520106</v>
       </c>
       <c r="R6" t="n">
-        <v>6967588</v>
+        <v>6967615</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1173,6 +1168,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1191,10 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119839397</v>
+        <v>119839399</v>
       </c>
       <c r="B7" t="n">
-        <v>100080</v>
+        <v>91494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,21 +1203,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1231,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520153</v>
+        <v>520154</v>
       </c>
       <c r="R7" t="n">
-        <v>6967764</v>
+        <v>6967747</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1275,7 +1271,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1294,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119839399</v>
+        <v>119839577</v>
       </c>
       <c r="B8" t="n">
-        <v>91494</v>
+        <v>90562</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1306,25 +1301,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1334,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520154</v>
+        <v>520121</v>
       </c>
       <c r="R8" t="n">
-        <v>6967747</v>
+        <v>6967669</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1396,10 +1391,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119839398</v>
+        <v>119839572</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>102825</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1408,25 +1403,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>222002</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1436,10 +1431,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520154</v>
+        <v>520020</v>
       </c>
       <c r="R9" t="n">
-        <v>6967747</v>
+        <v>6967619</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1498,10 +1493,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119839577</v>
+        <v>119839398</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1510,25 +1505,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1538,10 +1533,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520121</v>
+        <v>520154</v>
       </c>
       <c r="R10" t="n">
-        <v>6967669</v>
+        <v>6967747</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1600,10 +1595,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119839563</v>
+        <v>119839580</v>
       </c>
       <c r="B11" t="n">
-        <v>100080</v>
+        <v>100171</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1616,21 +1611,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1640,10 +1635,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520185</v>
+        <v>520045</v>
       </c>
       <c r="R11" t="n">
-        <v>6967760</v>
+        <v>6967714</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1684,7 +1679,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1703,10 +1697,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119839579</v>
+        <v>119839566</v>
       </c>
       <c r="B12" t="n">
-        <v>100080</v>
+        <v>103418</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1719,16 +1713,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1743,10 +1737,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520067</v>
+        <v>520227</v>
       </c>
       <c r="R12" t="n">
-        <v>6967702</v>
+        <v>6967737</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1787,7 +1781,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1806,10 +1799,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119839396</v>
+        <v>119839397</v>
       </c>
       <c r="B13" t="n">
-        <v>103418</v>
+        <v>100080</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,16 +1815,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1846,10 +1839,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520139</v>
+        <v>520153</v>
       </c>
       <c r="R13" t="n">
-        <v>6967793</v>
+        <v>6967764</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1890,6 +1883,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1908,10 +1902,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839580</v>
+        <v>119839569</v>
       </c>
       <c r="B14" t="n">
-        <v>100171</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,25 +1914,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1942,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520045</v>
+        <v>520132</v>
       </c>
       <c r="R14" t="n">
-        <v>6967714</v>
+        <v>6967651</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1986,12 +1980,18 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>på asp</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839385</v>
+        <v>119839571</v>
       </c>
       <c r="B15" t="n">
-        <v>103418</v>
+        <v>100171</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520045</v>
+        <v>520020</v>
       </c>
       <c r="R15" t="n">
-        <v>6967714</v>
+        <v>6967619</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119839572</v>
+        <v>119839396</v>
       </c>
       <c r="B16" t="n">
-        <v>102825</v>
+        <v>103418</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,16 +2128,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222002</v>
+        <v>222412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520020</v>
+        <v>520139</v>
       </c>
       <c r="R16" t="n">
-        <v>6967619</v>
+        <v>6967793</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839571</v>
+        <v>119839390</v>
       </c>
       <c r="B17" t="n">
-        <v>100171</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,38 +2226,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520020</v>
+        <v>519992</v>
       </c>
       <c r="R17" t="n">
-        <v>6967619</v>
+        <v>6967862</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2290,6 +2294,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>varav 1 hane, den andra såg jag inte . Båda trummade</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2316,7 +2325,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119839574</v>
+        <v>119839386</v>
       </c>
       <c r="B18" t="n">
         <v>100080</v>
@@ -2356,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520106</v>
+        <v>520045</v>
       </c>
       <c r="R18" t="n">
-        <v>6967615</v>
+        <v>6967714</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2419,10 +2428,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839390</v>
+        <v>119839579</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>100080</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2431,42 +2440,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>222771</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519992</v>
+        <v>520067</v>
       </c>
       <c r="R19" t="n">
-        <v>6967862</v>
+        <v>6967702</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2501,17 +2506,13 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>varav 1 hane, den andra såg jag inte . Båda trummade</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2530,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839386</v>
+        <v>119839404</v>
       </c>
       <c r="B20" t="n">
-        <v>100080</v>
+        <v>100171</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2546,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520045</v>
+        <v>520154</v>
       </c>
       <c r="R20" t="n">
-        <v>6967714</v>
+        <v>6967747</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2614,7 +2615,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119839570</v>
+        <v>119839385</v>
       </c>
       <c r="B21" t="n">
-        <v>101074</v>
+        <v>103418</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,21 +2649,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520020</v>
+        <v>520045</v>
       </c>
       <c r="R21" t="n">
-        <v>6967619</v>
+        <v>6967714</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839403</v>
+        <v>119839563</v>
       </c>
       <c r="B2" t="n">
-        <v>101074</v>
+        <v>100080</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520154</v>
+        <v>520185</v>
       </c>
       <c r="R2" t="n">
-        <v>6967747</v>
+        <v>6967760</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,6 +759,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839563</v>
+        <v>119839403</v>
       </c>
       <c r="B3" t="n">
-        <v>100080</v>
+        <v>101074</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +794,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520185</v>
+        <v>520154</v>
       </c>
       <c r="R3" t="n">
-        <v>6967760</v>
+        <v>6967747</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,7 +862,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839563</v>
+        <v>119839403</v>
       </c>
       <c r="B2" t="n">
-        <v>100080</v>
+        <v>101074</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520185</v>
+        <v>520154</v>
       </c>
       <c r="R2" t="n">
-        <v>6967760</v>
+        <v>6967747</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -778,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839403</v>
+        <v>119839563</v>
       </c>
       <c r="B3" t="n">
-        <v>101074</v>
+        <v>100080</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520154</v>
+        <v>520185</v>
       </c>
       <c r="R3" t="n">
-        <v>6967747</v>
+        <v>6967760</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,6 +861,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839563</v>
+        <v>119839385</v>
       </c>
       <c r="B2" t="n">
-        <v>100080</v>
+        <v>103441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520185</v>
+        <v>520045</v>
       </c>
       <c r="R2" t="n">
-        <v>6967760</v>
+        <v>6967714</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -778,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839403</v>
+        <v>119839397</v>
       </c>
       <c r="B3" t="n">
-        <v>101074</v>
+        <v>100103</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520154</v>
+        <v>520153</v>
       </c>
       <c r="R3" t="n">
-        <v>6967747</v>
+        <v>6967764</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,6 +861,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,10 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119839570</v>
+        <v>119839398</v>
       </c>
       <c r="B4" t="n">
-        <v>101074</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -892,25 +892,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520020</v>
+        <v>520154</v>
       </c>
       <c r="R4" t="n">
-        <v>6967619</v>
+        <v>6967747</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -982,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119839573</v>
+        <v>119839404</v>
       </c>
       <c r="B5" t="n">
-        <v>101074</v>
+        <v>100194</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,21 +998,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520045</v>
+        <v>520154</v>
       </c>
       <c r="R5" t="n">
-        <v>6967588</v>
+        <v>6967747</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119839574</v>
+        <v>119839580</v>
       </c>
       <c r="B6" t="n">
-        <v>100080</v>
+        <v>100194</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520106</v>
+        <v>520045</v>
       </c>
       <c r="R6" t="n">
-        <v>6967615</v>
+        <v>6967714</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1168,7 +1168,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1187,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119839399</v>
+        <v>119839386</v>
       </c>
       <c r="B7" t="n">
-        <v>91494</v>
+        <v>100103</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1203,21 +1202,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1227,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520154</v>
+        <v>520045</v>
       </c>
       <c r="R7" t="n">
-        <v>6967747</v>
+        <v>6967714</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1271,6 +1270,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119839577</v>
+        <v>119839396</v>
       </c>
       <c r="B8" t="n">
-        <v>90562</v>
+        <v>103441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1301,25 +1301,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520121</v>
+        <v>520139</v>
       </c>
       <c r="R8" t="n">
-        <v>6967669</v>
+        <v>6967793</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119839572</v>
+        <v>119839563</v>
       </c>
       <c r="B9" t="n">
-        <v>102825</v>
+        <v>100103</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1407,16 +1407,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222002</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520020</v>
+        <v>520185</v>
       </c>
       <c r="R9" t="n">
-        <v>6967619</v>
+        <v>6967760</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1475,6 +1475,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1493,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119839398</v>
+        <v>119839403</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>101097</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1505,25 +1506,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221235</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1595,10 +1596,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119839580</v>
+        <v>119839570</v>
       </c>
       <c r="B11" t="n">
-        <v>100171</v>
+        <v>101097</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1611,21 +1612,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1635,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520045</v>
+        <v>520020</v>
       </c>
       <c r="R11" t="n">
-        <v>6967714</v>
+        <v>6967619</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1697,10 +1698,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119839566</v>
+        <v>119839569</v>
       </c>
       <c r="B12" t="n">
-        <v>103418</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1709,25 +1710,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1737,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520227</v>
+        <v>520132</v>
       </c>
       <c r="R12" t="n">
-        <v>6967737</v>
+        <v>6967651</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1775,12 +1776,18 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>på asp</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1799,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119839397</v>
+        <v>119839573</v>
       </c>
       <c r="B13" t="n">
-        <v>100080</v>
+        <v>101097</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1815,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1839,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520153</v>
+        <v>520045</v>
       </c>
       <c r="R13" t="n">
-        <v>6967764</v>
+        <v>6967588</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1883,7 +1890,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1902,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839569</v>
+        <v>119839566</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>103441</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1914,25 +1920,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>222412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1942,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520132</v>
+        <v>520227</v>
       </c>
       <c r="R14" t="n">
-        <v>6967651</v>
+        <v>6967737</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1980,18 +1986,12 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>på asp</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839571</v>
+        <v>119839390</v>
       </c>
       <c r="B15" t="n">
-        <v>100171</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,38 +2022,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520020</v>
+        <v>519992</v>
       </c>
       <c r="R15" t="n">
-        <v>6967619</v>
+        <v>6967862</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2086,6 +2090,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>varav 1 hane, den andra såg jag inte . Båda trummade</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2112,10 +2121,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119839396</v>
+        <v>119839572</v>
       </c>
       <c r="B16" t="n">
-        <v>103418</v>
+        <v>102848</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,16 +2137,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>222002</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2152,10 +2161,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520139</v>
+        <v>520020</v>
       </c>
       <c r="R16" t="n">
-        <v>6967793</v>
+        <v>6967619</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2214,10 +2223,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839390</v>
+        <v>119839571</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>100194</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,42 +2235,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519992</v>
+        <v>520020</v>
       </c>
       <c r="R17" t="n">
-        <v>6967862</v>
+        <v>6967619</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2294,11 +2299,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>varav 1 hane, den andra såg jag inte . Båda trummade</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2325,10 +2325,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119839386</v>
+        <v>119839574</v>
       </c>
       <c r="B18" t="n">
-        <v>100080</v>
+        <v>100103</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520045</v>
+        <v>520106</v>
       </c>
       <c r="R18" t="n">
-        <v>6967714</v>
+        <v>6967615</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2428,10 +2428,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839579</v>
+        <v>119839399</v>
       </c>
       <c r="B19" t="n">
-        <v>100080</v>
+        <v>91512</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2444,21 +2444,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520067</v>
+        <v>520154</v>
       </c>
       <c r="R19" t="n">
-        <v>6967702</v>
+        <v>6967747</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2512,7 +2512,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2531,10 +2530,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839404</v>
+        <v>119839577</v>
       </c>
       <c r="B20" t="n">
-        <v>100171</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2543,25 +2542,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520154</v>
+        <v>520121</v>
       </c>
       <c r="R20" t="n">
-        <v>6967747</v>
+        <v>6967669</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2633,10 +2632,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119839385</v>
+        <v>119839579</v>
       </c>
       <c r="B21" t="n">
-        <v>103418</v>
+        <v>100103</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,16 +2648,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2673,10 +2672,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520045</v>
+        <v>520067</v>
       </c>
       <c r="R21" t="n">
-        <v>6967714</v>
+        <v>6967702</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2717,6 +2716,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839385</v>
+        <v>119839571</v>
       </c>
       <c r="B2" t="n">
-        <v>103441</v>
+        <v>100194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520045</v>
+        <v>520020</v>
       </c>
       <c r="R2" t="n">
-        <v>6967714</v>
+        <v>6967619</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -880,10 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119839398</v>
+        <v>119839396</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>103441</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -892,25 +892,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520154</v>
+        <v>520139</v>
       </c>
       <c r="R4" t="n">
-        <v>6967747</v>
+        <v>6967793</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -982,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119839404</v>
+        <v>119839403</v>
       </c>
       <c r="B5" t="n">
-        <v>100194</v>
+        <v>101097</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,21 +998,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119839580</v>
+        <v>119839579</v>
       </c>
       <c r="B6" t="n">
-        <v>100194</v>
+        <v>100103</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520045</v>
+        <v>520067</v>
       </c>
       <c r="R6" t="n">
-        <v>6967714</v>
+        <v>6967702</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1168,6 +1168,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1186,10 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119839386</v>
+        <v>119839404</v>
       </c>
       <c r="B7" t="n">
-        <v>100103</v>
+        <v>100194</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,21 +1203,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1226,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520045</v>
+        <v>520154</v>
       </c>
       <c r="R7" t="n">
-        <v>6967714</v>
+        <v>6967747</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1270,7 +1271,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119839396</v>
+        <v>119839390</v>
       </c>
       <c r="B8" t="n">
-        <v>103441</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1301,38 +1301,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520139</v>
+        <v>519992</v>
       </c>
       <c r="R8" t="n">
-        <v>6967793</v>
+        <v>6967862</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1365,6 +1369,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>varav 1 hane, den andra såg jag inte . Båda trummade</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,10 +1400,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119839563</v>
+        <v>119839573</v>
       </c>
       <c r="B9" t="n">
-        <v>100103</v>
+        <v>101097</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1407,21 +1416,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1431,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520185</v>
+        <v>520045</v>
       </c>
       <c r="R9" t="n">
-        <v>6967760</v>
+        <v>6967588</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1475,7 +1484,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1494,10 +1502,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119839403</v>
+        <v>119839572</v>
       </c>
       <c r="B10" t="n">
-        <v>101097</v>
+        <v>102848</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1510,21 +1518,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221235</v>
+        <v>222002</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1534,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520154</v>
+        <v>520020</v>
       </c>
       <c r="R10" t="n">
-        <v>6967747</v>
+        <v>6967619</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1596,10 +1604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119839570</v>
+        <v>119839385</v>
       </c>
       <c r="B11" t="n">
-        <v>101097</v>
+        <v>103441</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1612,21 +1620,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520020</v>
+        <v>520045</v>
       </c>
       <c r="R11" t="n">
-        <v>6967619</v>
+        <v>6967714</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1698,10 +1706,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119839569</v>
+        <v>119839399</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>91512</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1710,25 +1718,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1738,10 +1746,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520132</v>
+        <v>520154</v>
       </c>
       <c r="R12" t="n">
-        <v>6967651</v>
+        <v>6967747</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1776,18 +1784,12 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>på asp</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1806,10 +1808,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119839573</v>
+        <v>119839566</v>
       </c>
       <c r="B13" t="n">
-        <v>101097</v>
+        <v>103441</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1824,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1848,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520045</v>
+        <v>520227</v>
       </c>
       <c r="R13" t="n">
-        <v>6967588</v>
+        <v>6967737</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1908,10 +1910,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839566</v>
+        <v>119839580</v>
       </c>
       <c r="B14" t="n">
-        <v>103441</v>
+        <v>100194</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1926,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520227</v>
+        <v>520045</v>
       </c>
       <c r="R14" t="n">
-        <v>6967737</v>
+        <v>6967714</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2010,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839390</v>
+        <v>119839570</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>101097</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,42 +2024,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>221235</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519992</v>
+        <v>520020</v>
       </c>
       <c r="R15" t="n">
-        <v>6967862</v>
+        <v>6967619</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2090,11 +2088,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>varav 1 hane, den andra såg jag inte . Båda trummade</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2121,10 +2114,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119839572</v>
+        <v>119839569</v>
       </c>
       <c r="B16" t="n">
-        <v>102848</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2133,25 +2126,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222002</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2161,10 +2154,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520020</v>
+        <v>520132</v>
       </c>
       <c r="R16" t="n">
-        <v>6967619</v>
+        <v>6967651</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2199,12 +2192,18 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>på asp</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2223,10 +2222,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839571</v>
+        <v>119839563</v>
       </c>
       <c r="B17" t="n">
-        <v>100194</v>
+        <v>100103</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2239,21 +2238,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2263,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520020</v>
+        <v>520185</v>
       </c>
       <c r="R17" t="n">
-        <v>6967619</v>
+        <v>6967760</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2307,6 +2306,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2325,10 +2325,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119839574</v>
+        <v>119839398</v>
       </c>
       <c r="B18" t="n">
-        <v>100103</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2337,25 +2337,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520106</v>
+        <v>520154</v>
       </c>
       <c r="R18" t="n">
-        <v>6967615</v>
+        <v>6967747</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2409,7 +2409,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2428,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839399</v>
+        <v>119839574</v>
       </c>
       <c r="B19" t="n">
-        <v>91512</v>
+        <v>100103</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2444,21 +2443,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2468,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520154</v>
+        <v>520106</v>
       </c>
       <c r="R19" t="n">
-        <v>6967747</v>
+        <v>6967615</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2512,6 +2511,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839577</v>
+        <v>119839386</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>100103</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,25 +2542,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520121</v>
+        <v>520045</v>
       </c>
       <c r="R20" t="n">
-        <v>6967669</v>
+        <v>6967714</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2614,6 +2614,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2632,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119839579</v>
+        <v>119839577</v>
       </c>
       <c r="B21" t="n">
-        <v>100103</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2644,25 +2645,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2672,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520067</v>
+        <v>520121</v>
       </c>
       <c r="R21" t="n">
-        <v>6967702</v>
+        <v>6967669</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2716,7 +2717,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -982,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119839403</v>
+        <v>119839579</v>
       </c>
       <c r="B5" t="n">
-        <v>101097</v>
+        <v>100103</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,21 +998,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520154</v>
+        <v>520067</v>
       </c>
       <c r="R5" t="n">
-        <v>6967747</v>
+        <v>6967702</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,6 +1066,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1084,10 +1085,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119839579</v>
+        <v>119839403</v>
       </c>
       <c r="B6" t="n">
-        <v>100103</v>
+        <v>101097</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,21 +1101,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520067</v>
+        <v>520154</v>
       </c>
       <c r="R6" t="n">
-        <v>6967702</v>
+        <v>6967747</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1168,7 +1169,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839571</v>
+        <v>119839570</v>
       </c>
       <c r="B2" t="n">
-        <v>100194</v>
+        <v>101097</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839397</v>
+        <v>119839577</v>
       </c>
       <c r="B3" t="n">
-        <v>100103</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520153</v>
+        <v>520121</v>
       </c>
       <c r="R3" t="n">
-        <v>6967764</v>
+        <v>6967669</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,7 +861,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119839396</v>
+        <v>119839573</v>
       </c>
       <c r="B4" t="n">
-        <v>103441</v>
+        <v>101097</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520139</v>
+        <v>520045</v>
       </c>
       <c r="R4" t="n">
-        <v>6967793</v>
+        <v>6967588</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -982,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119839579</v>
+        <v>119839399</v>
       </c>
       <c r="B5" t="n">
-        <v>100103</v>
+        <v>91512</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1022,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520067</v>
+        <v>520154</v>
       </c>
       <c r="R5" t="n">
-        <v>6967702</v>
+        <v>6967747</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1065,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1085,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119839403</v>
+        <v>119839386</v>
       </c>
       <c r="B6" t="n">
-        <v>101097</v>
+        <v>100103</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1101,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1125,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520154</v>
+        <v>520045</v>
       </c>
       <c r="R6" t="n">
-        <v>6967747</v>
+        <v>6967714</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1169,6 +1167,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1187,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119839404</v>
+        <v>119839572</v>
       </c>
       <c r="B7" t="n">
-        <v>100194</v>
+        <v>102848</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1203,21 +1202,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1227,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520154</v>
+        <v>520020</v>
       </c>
       <c r="R7" t="n">
-        <v>6967747</v>
+        <v>6967619</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1289,10 +1288,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119839390</v>
+        <v>119839385</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>103441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1301,42 +1300,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519992</v>
+        <v>520045</v>
       </c>
       <c r="R8" t="n">
-        <v>6967862</v>
+        <v>6967714</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1369,11 +1364,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>varav 1 hane, den andra såg jag inte . Båda trummade</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1400,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119839573</v>
+        <v>119839404</v>
       </c>
       <c r="B9" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,21 +1406,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1440,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520045</v>
+        <v>520154</v>
       </c>
       <c r="R9" t="n">
-        <v>6967588</v>
+        <v>6967747</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1502,10 +1492,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119839572</v>
+        <v>119839580</v>
       </c>
       <c r="B10" t="n">
-        <v>102848</v>
+        <v>100194</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,21 +1508,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1542,10 +1532,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520020</v>
+        <v>520045</v>
       </c>
       <c r="R10" t="n">
-        <v>6967619</v>
+        <v>6967714</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1604,7 +1594,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119839385</v>
+        <v>119839566</v>
       </c>
       <c r="B11" t="n">
         <v>103441</v>
@@ -1644,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520045</v>
+        <v>520227</v>
       </c>
       <c r="R11" t="n">
-        <v>6967714</v>
+        <v>6967737</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1706,10 +1696,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119839399</v>
+        <v>119839390</v>
       </c>
       <c r="B12" t="n">
-        <v>91512</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1718,38 +1708,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520154</v>
+        <v>519992</v>
       </c>
       <c r="R12" t="n">
-        <v>6967747</v>
+        <v>6967862</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1782,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>varav 1 hane, den andra såg jag inte . Båda trummade</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1808,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119839566</v>
+        <v>119839574</v>
       </c>
       <c r="B13" t="n">
-        <v>103441</v>
+        <v>100103</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,16 +1823,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1848,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520227</v>
+        <v>520106</v>
       </c>
       <c r="R13" t="n">
-        <v>6967737</v>
+        <v>6967615</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1892,6 +1891,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119839580</v>
+        <v>119839579</v>
       </c>
       <c r="B14" t="n">
-        <v>100194</v>
+        <v>100103</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,21 +1926,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520045</v>
+        <v>520067</v>
       </c>
       <c r="R14" t="n">
-        <v>6967714</v>
+        <v>6967702</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1994,6 +1994,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2012,10 +2013,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119839570</v>
+        <v>119839569</v>
       </c>
       <c r="B15" t="n">
-        <v>101097</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2024,25 +2025,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2052,10 +2053,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520020</v>
+        <v>520132</v>
       </c>
       <c r="R15" t="n">
-        <v>6967619</v>
+        <v>6967651</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2090,12 +2091,18 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>på asp</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2114,10 +2121,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119839569</v>
+        <v>119839397</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>100103</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2126,25 +2133,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2154,10 +2161,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520132</v>
+        <v>520153</v>
       </c>
       <c r="R16" t="n">
-        <v>6967651</v>
+        <v>6967764</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2190,11 +2197,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>på asp</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2222,10 +2224,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839563</v>
+        <v>119839403</v>
       </c>
       <c r="B17" t="n">
-        <v>100103</v>
+        <v>101097</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2238,21 +2240,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2262,10 +2264,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520185</v>
+        <v>520154</v>
       </c>
       <c r="R17" t="n">
-        <v>6967760</v>
+        <v>6967747</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2306,7 +2308,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2325,10 +2326,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119839398</v>
+        <v>119839571</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>100194</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2337,25 +2338,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2365,10 +2366,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520154</v>
+        <v>520020</v>
       </c>
       <c r="R18" t="n">
-        <v>6967747</v>
+        <v>6967619</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2427,10 +2428,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839574</v>
+        <v>119839396</v>
       </c>
       <c r="B19" t="n">
-        <v>100103</v>
+        <v>103441</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2443,16 +2444,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2467,10 +2468,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520106</v>
+        <v>520139</v>
       </c>
       <c r="R19" t="n">
-        <v>6967615</v>
+        <v>6967793</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2511,7 +2512,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119839386</v>
+        <v>119839398</v>
       </c>
       <c r="B20" t="n">
-        <v>100103</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,25 +2542,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520045</v>
+        <v>520154</v>
       </c>
       <c r="R20" t="n">
-        <v>6967714</v>
+        <v>6967747</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2614,7 +2614,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2633,10 +2632,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119839577</v>
+        <v>119839563</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>100103</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2645,25 +2644,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2672,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520121</v>
+        <v>520185</v>
       </c>
       <c r="R21" t="n">
-        <v>6967669</v>
+        <v>6967760</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2717,6 +2716,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -2121,10 +2121,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119839397</v>
+        <v>119839571</v>
       </c>
       <c r="B16" t="n">
-        <v>100103</v>
+        <v>100194</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2137,21 +2137,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520153</v>
+        <v>520020</v>
       </c>
       <c r="R16" t="n">
-        <v>6967764</v>
+        <v>6967619</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2205,7 +2205,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2224,10 +2223,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119839403</v>
+        <v>119839396</v>
       </c>
       <c r="B17" t="n">
-        <v>101097</v>
+        <v>103441</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2240,21 +2239,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2264,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520154</v>
+        <v>520139</v>
       </c>
       <c r="R17" t="n">
-        <v>6967747</v>
+        <v>6967793</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2326,10 +2325,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119839571</v>
+        <v>119839397</v>
       </c>
       <c r="B18" t="n">
-        <v>100194</v>
+        <v>100103</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2342,21 +2341,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2366,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520020</v>
+        <v>520153</v>
       </c>
       <c r="R18" t="n">
-        <v>6967619</v>
+        <v>6967764</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2410,6 +2409,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2428,10 +2428,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119839396</v>
+        <v>119839403</v>
       </c>
       <c r="B19" t="n">
-        <v>103441</v>
+        <v>101097</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2444,21 +2444,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520139</v>
+        <v>520154</v>
       </c>
       <c r="R19" t="n">
-        <v>6967793</v>
+        <v>6967747</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2733,6 +2733,2796 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121477474</v>
+      </c>
+      <c r="B22" t="n">
+        <v>90709</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>519997</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6967748</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121481704</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>520220</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6967703</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121481732</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>520278</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6967715</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121481332</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>520108</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6967640</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121481691</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79686</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>520232</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6967691</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121481563</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>520152</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6967652</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121481558</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79686</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>520195</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6967685</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121478200</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>519995</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6967827</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121481087</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>520115</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6967640</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121481479</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>520117</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6967650</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121481572</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>520158</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6967663</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>121480924</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>520122</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6967652</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>121478601</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Långmyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>519990</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6967852</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>121481619</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>520190</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6967698</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>121481678</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79686</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>520220</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6967688</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>121481699</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>520237</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6967698</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>121481677</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>520234</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6967703</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>121481685</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>520238</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6967692</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>121481758</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>520254</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6967738</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>121481742</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>520275</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6967730</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>121476235</v>
+      </c>
+      <c r="B42" t="n">
+        <v>90709</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>519974</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6967729</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>121479853</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>520028</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6967759</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>121481637</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>520215</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6967683</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>121481738</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>520268</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6967719</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>121481595</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>520162</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6967675</v>
+      </c>
+      <c r="S46" t="n">
+        <v>20</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121477474</v>
+        <v>121481678</v>
       </c>
       <c r="B22" t="n">
-        <v>90709</v>
+        <v>79686</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519997</v>
+        <v>520220</v>
       </c>
       <c r="R22" t="n">
-        <v>6967748</v>
+        <v>6967688</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,7 +2847,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121481704</v>
+        <v>121481572</v>
       </c>
       <c r="B23" t="n">
         <v>79685</v>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520220</v>
+        <v>520158</v>
       </c>
       <c r="R23" t="n">
-        <v>6967703</v>
+        <v>6967663</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2959,7 +2959,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121481732</v>
+        <v>121481619</v>
       </c>
       <c r="B24" t="n">
         <v>79685</v>
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520278</v>
+        <v>520190</v>
       </c>
       <c r="R24" t="n">
-        <v>6967715</v>
+        <v>6967698</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3071,7 +3071,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121481332</v>
+        <v>121481732</v>
       </c>
       <c r="B25" t="n">
         <v>79685</v>
@@ -3111,13 +3111,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520108</v>
+        <v>520278</v>
       </c>
       <c r="R25" t="n">
-        <v>6967640</v>
+        <v>6967715</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,10 +3183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121481691</v>
+        <v>121481758</v>
       </c>
       <c r="B26" t="n">
-        <v>79686</v>
+        <v>79685</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3199,21 +3199,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520232</v>
+        <v>520254</v>
       </c>
       <c r="R26" t="n">
-        <v>6967691</v>
+        <v>6967738</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3295,7 +3295,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121481563</v>
+        <v>121480924</v>
       </c>
       <c r="B27" t="n">
         <v>79685</v>
@@ -3335,13 +3335,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520152</v>
+        <v>520122</v>
       </c>
       <c r="R27" t="n">
         <v>6967652</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3407,10 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121481558</v>
+        <v>121478200</v>
       </c>
       <c r="B28" t="n">
-        <v>79686</v>
+        <v>79685</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520195</v>
+        <v>519995</v>
       </c>
       <c r="R28" t="n">
-        <v>6967685</v>
+        <v>6967827</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3480,9 +3480,19 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3509,10 +3519,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121478200</v>
+        <v>121477474</v>
       </c>
       <c r="B29" t="n">
-        <v>79685</v>
+        <v>90710</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3525,21 +3535,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3549,10 +3559,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519995</v>
+        <v>519997</v>
       </c>
       <c r="R29" t="n">
-        <v>6967827</v>
+        <v>6967748</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3584,7 +3594,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3594,7 +3604,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3621,7 +3631,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121481087</v>
+        <v>121481637</v>
       </c>
       <c r="B30" t="n">
         <v>79685</v>
@@ -3661,13 +3671,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520115</v>
+        <v>520215</v>
       </c>
       <c r="R30" t="n">
-        <v>6967640</v>
+        <v>6967683</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3696,7 +3706,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3706,7 +3716,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3733,10 +3743,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121481479</v>
+        <v>121481558</v>
       </c>
       <c r="B31" t="n">
-        <v>79685</v>
+        <v>79686</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3749,21 +3759,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3773,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520117</v>
+        <v>520195</v>
       </c>
       <c r="R31" t="n">
-        <v>6967650</v>
+        <v>6967685</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3806,19 +3816,9 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3845,7 +3845,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121481572</v>
+        <v>121478601</v>
       </c>
       <c r="B32" t="n">
         <v>79685</v>
@@ -3881,17 +3881,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+          <t>Långmyrberget, Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520158</v>
+        <v>519990</v>
       </c>
       <c r="R32" t="n">
-        <v>6967663</v>
+        <v>6967852</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3957,7 +3957,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121480924</v>
+        <v>121481742</v>
       </c>
       <c r="B33" t="n">
         <v>79685</v>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520122</v>
+        <v>520275</v>
       </c>
       <c r="R33" t="n">
-        <v>6967652</v>
+        <v>6967730</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,7 +4069,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121478601</v>
+        <v>121481699</v>
       </c>
       <c r="B34" t="n">
         <v>79685</v>
@@ -4105,17 +4105,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långmyrberget, Långmyrberget, Jmt</t>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519990</v>
+        <v>520237</v>
       </c>
       <c r="R34" t="n">
-        <v>6967852</v>
+        <v>6967698</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4181,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121481619</v>
+        <v>121476235</v>
       </c>
       <c r="B35" t="n">
-        <v>79685</v>
+        <v>90710</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4197,21 +4197,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4221,10 +4221,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520190</v>
+        <v>519974</v>
       </c>
       <c r="R35" t="n">
-        <v>6967698</v>
+        <v>6967729</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4293,7 +4293,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121481678</v>
+        <v>121481691</v>
       </c>
       <c r="B36" t="n">
         <v>79686</v>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520220</v>
+        <v>520232</v>
       </c>
       <c r="R36" t="n">
-        <v>6967688</v>
+        <v>6967691</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4405,7 +4405,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121481699</v>
+        <v>121481087</v>
       </c>
       <c r="B37" t="n">
         <v>79685</v>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520237</v>
+        <v>520115</v>
       </c>
       <c r="R37" t="n">
-        <v>6967698</v>
+        <v>6967640</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,7 +4517,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121481677</v>
+        <v>121481479</v>
       </c>
       <c r="B38" t="n">
         <v>79685</v>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520234</v>
+        <v>520117</v>
       </c>
       <c r="R38" t="n">
-        <v>6967703</v>
+        <v>6967650</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4629,7 +4629,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121481685</v>
+        <v>121481595</v>
       </c>
       <c r="B39" t="n">
         <v>79685</v>
@@ -4669,13 +4669,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520238</v>
+        <v>520162</v>
       </c>
       <c r="R39" t="n">
-        <v>6967692</v>
+        <v>6967675</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,7 +4741,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121481758</v>
+        <v>121481738</v>
       </c>
       <c r="B40" t="n">
         <v>79685</v>
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>520254</v>
+        <v>520268</v>
       </c>
       <c r="R40" t="n">
-        <v>6967738</v>
+        <v>6967719</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,7 +4853,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121481742</v>
+        <v>121481704</v>
       </c>
       <c r="B41" t="n">
         <v>79685</v>
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520275</v>
+        <v>520220</v>
       </c>
       <c r="R41" t="n">
-        <v>6967730</v>
+        <v>6967703</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4965,10 +4965,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121476235</v>
+        <v>121479853</v>
       </c>
       <c r="B42" t="n">
-        <v>90709</v>
+        <v>79685</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4981,21 +4981,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519974</v>
+        <v>520028</v>
       </c>
       <c r="R42" t="n">
-        <v>6967729</v>
+        <v>6967759</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5077,7 +5077,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121479853</v>
+        <v>121481677</v>
       </c>
       <c r="B43" t="n">
         <v>79685</v>
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520028</v>
+        <v>520234</v>
       </c>
       <c r="R43" t="n">
-        <v>6967759</v>
+        <v>6967703</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5189,7 +5189,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121481637</v>
+        <v>121481563</v>
       </c>
       <c r="B44" t="n">
         <v>79685</v>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520215</v>
+        <v>520152</v>
       </c>
       <c r="R44" t="n">
-        <v>6967683</v>
+        <v>6967652</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5301,7 +5301,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121481738</v>
+        <v>121481332</v>
       </c>
       <c r="B45" t="n">
         <v>79685</v>
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520268</v>
+        <v>520108</v>
       </c>
       <c r="R45" t="n">
-        <v>6967719</v>
+        <v>6967640</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5413,7 +5413,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121481595</v>
+        <v>121481685</v>
       </c>
       <c r="B46" t="n">
         <v>79685</v>
@@ -5453,13 +5453,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520162</v>
+        <v>520238</v>
       </c>
       <c r="R46" t="n">
-        <v>6967675</v>
+        <v>6967692</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121481678</v>
+        <v>121481332</v>
       </c>
       <c r="B22" t="n">
-        <v>79686</v>
+        <v>79688</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520220</v>
+        <v>520108</v>
       </c>
       <c r="R22" t="n">
-        <v>6967688</v>
+        <v>6967640</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2850,7 +2850,7 @@
         <v>121481572</v>
       </c>
       <c r="B23" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2959,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121481619</v>
+        <v>121481558</v>
       </c>
       <c r="B24" t="n">
-        <v>79685</v>
+        <v>79689</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2975,21 +2975,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520190</v>
+        <v>520195</v>
       </c>
       <c r="R24" t="n">
-        <v>6967698</v>
+        <v>6967685</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3032,19 +3032,9 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3071,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121481732</v>
+        <v>121481678</v>
       </c>
       <c r="B25" t="n">
-        <v>79685</v>
+        <v>79689</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3087,21 +3077,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3111,13 +3101,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520278</v>
+        <v>520220</v>
       </c>
       <c r="R25" t="n">
-        <v>6967715</v>
+        <v>6967688</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3146,7 +3136,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3156,7 +3146,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,10 +3173,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121481758</v>
+        <v>121481738</v>
       </c>
       <c r="B26" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3223,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520254</v>
+        <v>520268</v>
       </c>
       <c r="R26" t="n">
-        <v>6967738</v>
+        <v>6967719</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3258,7 +3248,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3268,7 +3258,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3295,10 +3285,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121480924</v>
+        <v>121481563</v>
       </c>
       <c r="B27" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3335,13 +3325,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520122</v>
+        <v>520152</v>
       </c>
       <c r="R27" t="n">
         <v>6967652</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3370,7 +3360,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3380,7 +3370,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3407,10 +3397,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121478200</v>
+        <v>121476235</v>
       </c>
       <c r="B28" t="n">
-        <v>79685</v>
+        <v>90713</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3423,21 +3413,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,13 +3437,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519995</v>
+        <v>519974</v>
       </c>
       <c r="R28" t="n">
-        <v>6967827</v>
+        <v>6967729</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3482,7 +3472,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3492,7 +3482,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3522,7 +3512,7 @@
         <v>121477474</v>
       </c>
       <c r="B29" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3631,10 +3621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121481637</v>
+        <v>121481758</v>
       </c>
       <c r="B30" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3671,13 +3661,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520215</v>
+        <v>520254</v>
       </c>
       <c r="R30" t="n">
-        <v>6967683</v>
+        <v>6967738</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3706,7 +3696,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3716,7 +3706,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3743,10 +3733,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121481558</v>
+        <v>121481699</v>
       </c>
       <c r="B31" t="n">
-        <v>79686</v>
+        <v>79688</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3759,21 +3749,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3783,10 +3773,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520195</v>
+        <v>520237</v>
       </c>
       <c r="R31" t="n">
-        <v>6967685</v>
+        <v>6967698</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3816,9 +3806,19 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3845,10 +3845,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121478601</v>
+        <v>121481732</v>
       </c>
       <c r="B32" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3881,14 +3881,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långmyrberget, Långmyrberget, Jmt</t>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519990</v>
+        <v>520278</v>
       </c>
       <c r="R32" t="n">
-        <v>6967852</v>
+        <v>6967715</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3957,10 +3957,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121481742</v>
+        <v>121481677</v>
       </c>
       <c r="B33" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520275</v>
+        <v>520234</v>
       </c>
       <c r="R33" t="n">
-        <v>6967730</v>
+        <v>6967703</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121481699</v>
+        <v>121481619</v>
       </c>
       <c r="B34" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520237</v>
+        <v>520190</v>
       </c>
       <c r="R34" t="n">
         <v>6967698</v>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4181,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121476235</v>
+        <v>121478601</v>
       </c>
       <c r="B35" t="n">
-        <v>90710</v>
+        <v>79688</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4197,37 +4197,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+          <t>Långmyrberget, Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519974</v>
+        <v>519990</v>
       </c>
       <c r="R35" t="n">
-        <v>6967729</v>
+        <v>6967852</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4293,10 +4293,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121481691</v>
+        <v>121481479</v>
       </c>
       <c r="B36" t="n">
-        <v>79686</v>
+        <v>79688</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4309,21 +4309,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520232</v>
+        <v>520117</v>
       </c>
       <c r="R36" t="n">
-        <v>6967691</v>
+        <v>6967650</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4405,10 +4405,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121481087</v>
+        <v>121481685</v>
       </c>
       <c r="B37" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520115</v>
+        <v>520238</v>
       </c>
       <c r="R37" t="n">
-        <v>6967640</v>
+        <v>6967692</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,10 +4517,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121481479</v>
+        <v>121480924</v>
       </c>
       <c r="B38" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520117</v>
+        <v>520122</v>
       </c>
       <c r="R38" t="n">
-        <v>6967650</v>
+        <v>6967652</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4629,10 +4629,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121481595</v>
+        <v>121481742</v>
       </c>
       <c r="B39" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4669,13 +4669,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520162</v>
+        <v>520275</v>
       </c>
       <c r="R39" t="n">
-        <v>6967675</v>
+        <v>6967730</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121481738</v>
+        <v>121481704</v>
       </c>
       <c r="B40" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>520268</v>
+        <v>520220</v>
       </c>
       <c r="R40" t="n">
-        <v>6967719</v>
+        <v>6967703</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,10 +4853,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121481704</v>
+        <v>121479853</v>
       </c>
       <c r="B41" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520220</v>
+        <v>520028</v>
       </c>
       <c r="R41" t="n">
-        <v>6967703</v>
+        <v>6967759</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4965,10 +4965,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121479853</v>
+        <v>121481595</v>
       </c>
       <c r="B42" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5005,13 +5005,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520028</v>
+        <v>520162</v>
       </c>
       <c r="R42" t="n">
-        <v>6967759</v>
+        <v>6967675</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5077,10 +5077,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121481677</v>
+        <v>121481637</v>
       </c>
       <c r="B43" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5117,13 +5117,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520234</v>
+        <v>520215</v>
       </c>
       <c r="R43" t="n">
-        <v>6967703</v>
+        <v>6967683</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5189,10 +5189,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121481563</v>
+        <v>121481691</v>
       </c>
       <c r="B44" t="n">
-        <v>79685</v>
+        <v>79689</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5205,21 +5205,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5229,13 +5229,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520152</v>
+        <v>520232</v>
       </c>
       <c r="R44" t="n">
-        <v>6967652</v>
+        <v>6967691</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5301,10 +5301,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121481332</v>
+        <v>121478200</v>
       </c>
       <c r="B45" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5341,13 +5341,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520108</v>
+        <v>519995</v>
       </c>
       <c r="R45" t="n">
-        <v>6967640</v>
+        <v>6967827</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5413,10 +5413,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121481685</v>
+        <v>121481087</v>
       </c>
       <c r="B46" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520238</v>
+        <v>520115</v>
       </c>
       <c r="R46" t="n">
-        <v>6967692</v>
+        <v>6967640</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -2735,7 +2735,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121481332</v>
+        <v>121481479</v>
       </c>
       <c r="B22" t="n">
         <v>79688</v>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520108</v>
+        <v>520117</v>
       </c>
       <c r="R22" t="n">
-        <v>6967640</v>
+        <v>6967650</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121481572</v>
+        <v>121477474</v>
       </c>
       <c r="B23" t="n">
-        <v>79688</v>
+        <v>90713</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2863,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520158</v>
+        <v>519997</v>
       </c>
       <c r="R23" t="n">
-        <v>6967663</v>
+        <v>6967748</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2959,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121481558</v>
+        <v>121480924</v>
       </c>
       <c r="B24" t="n">
-        <v>79689</v>
+        <v>79688</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2975,21 +2975,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520195</v>
+        <v>520122</v>
       </c>
       <c r="R24" t="n">
-        <v>6967685</v>
+        <v>6967652</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3032,9 +3032,19 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,10 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121481678</v>
+        <v>121476235</v>
       </c>
       <c r="B25" t="n">
-        <v>79689</v>
+        <v>90713</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3077,21 +3087,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3101,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520220</v>
+        <v>519974</v>
       </c>
       <c r="R25" t="n">
-        <v>6967688</v>
+        <v>6967729</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3136,7 +3146,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3146,7 +3156,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3173,7 +3183,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121481738</v>
+        <v>121481087</v>
       </c>
       <c r="B26" t="n">
         <v>79688</v>
@@ -3213,10 +3223,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520268</v>
+        <v>520115</v>
       </c>
       <c r="R26" t="n">
-        <v>6967719</v>
+        <v>6967640</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3248,7 +3258,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3258,7 +3268,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3397,10 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121476235</v>
+        <v>121481677</v>
       </c>
       <c r="B28" t="n">
-        <v>90713</v>
+        <v>79688</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3413,21 +3423,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3447,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519974</v>
+        <v>520234</v>
       </c>
       <c r="R28" t="n">
-        <v>6967729</v>
+        <v>6967703</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,7 +3482,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3482,7 +3492,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3509,10 +3519,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121477474</v>
+        <v>121481332</v>
       </c>
       <c r="B29" t="n">
-        <v>90713</v>
+        <v>79688</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3525,21 +3535,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3549,13 +3559,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519997</v>
+        <v>520108</v>
       </c>
       <c r="R29" t="n">
-        <v>6967748</v>
+        <v>6967640</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3584,7 +3594,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3594,7 +3604,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3621,7 +3631,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121481758</v>
+        <v>121481637</v>
       </c>
       <c r="B30" t="n">
         <v>79688</v>
@@ -3661,13 +3671,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520254</v>
+        <v>520215</v>
       </c>
       <c r="R30" t="n">
-        <v>6967738</v>
+        <v>6967683</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3696,7 +3706,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3706,7 +3716,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3733,7 +3743,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121481699</v>
+        <v>121481704</v>
       </c>
       <c r="B31" t="n">
         <v>79688</v>
@@ -3773,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520237</v>
+        <v>520220</v>
       </c>
       <c r="R31" t="n">
-        <v>6967698</v>
+        <v>6967703</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3808,7 +3818,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3818,7 +3828,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3845,7 +3855,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121481732</v>
+        <v>121481742</v>
       </c>
       <c r="B32" t="n">
         <v>79688</v>
@@ -3885,13 +3895,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520278</v>
+        <v>520275</v>
       </c>
       <c r="R32" t="n">
-        <v>6967715</v>
+        <v>6967730</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3920,7 +3930,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3930,7 +3940,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3957,7 +3967,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121481677</v>
+        <v>121479853</v>
       </c>
       <c r="B33" t="n">
         <v>79688</v>
@@ -3997,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520234</v>
+        <v>520028</v>
       </c>
       <c r="R33" t="n">
-        <v>6967703</v>
+        <v>6967759</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4032,7 +4042,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4052,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,7 +4079,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121481619</v>
+        <v>121478200</v>
       </c>
       <c r="B34" t="n">
         <v>79688</v>
@@ -4109,13 +4119,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520190</v>
+        <v>519995</v>
       </c>
       <c r="R34" t="n">
-        <v>6967698</v>
+        <v>6967827</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4144,7 +4154,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4154,7 +4164,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4293,7 +4303,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121481479</v>
+        <v>121481758</v>
       </c>
       <c r="B36" t="n">
         <v>79688</v>
@@ -4333,10 +4343,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520117</v>
+        <v>520254</v>
       </c>
       <c r="R36" t="n">
-        <v>6967650</v>
+        <v>6967738</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4368,7 +4378,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4378,7 +4388,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4405,7 +4415,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121481685</v>
+        <v>121481738</v>
       </c>
       <c r="B37" t="n">
         <v>79688</v>
@@ -4445,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520238</v>
+        <v>520268</v>
       </c>
       <c r="R37" t="n">
-        <v>6967692</v>
+        <v>6967719</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,7 +4527,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121480924</v>
+        <v>121481572</v>
       </c>
       <c r="B38" t="n">
         <v>79688</v>
@@ -4557,10 +4567,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520122</v>
+        <v>520158</v>
       </c>
       <c r="R38" t="n">
-        <v>6967652</v>
+        <v>6967663</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4592,7 +4602,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4602,7 +4612,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4629,10 +4639,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121481742</v>
+        <v>121481558</v>
       </c>
       <c r="B39" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4645,21 +4655,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4669,10 +4679,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520275</v>
+        <v>520195</v>
       </c>
       <c r="R39" t="n">
-        <v>6967730</v>
+        <v>6967685</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4702,19 +4712,9 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121481704</v>
+        <v>121481691</v>
       </c>
       <c r="B40" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4757,21 +4757,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>520220</v>
+        <v>520232</v>
       </c>
       <c r="R40" t="n">
-        <v>6967703</v>
+        <v>6967691</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,7 +4853,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121479853</v>
+        <v>121481699</v>
       </c>
       <c r="B41" t="n">
         <v>79688</v>
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520028</v>
+        <v>520237</v>
       </c>
       <c r="R41" t="n">
-        <v>6967759</v>
+        <v>6967698</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4965,7 +4965,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121481595</v>
+        <v>121481619</v>
       </c>
       <c r="B42" t="n">
         <v>79688</v>
@@ -5005,13 +5005,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520162</v>
+        <v>520190</v>
       </c>
       <c r="R42" t="n">
-        <v>6967675</v>
+        <v>6967698</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5077,7 +5077,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121481637</v>
+        <v>121481595</v>
       </c>
       <c r="B43" t="n">
         <v>79688</v>
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520215</v>
+        <v>520162</v>
       </c>
       <c r="R43" t="n">
-        <v>6967683</v>
+        <v>6967675</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5189,10 +5189,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121481691</v>
+        <v>121481732</v>
       </c>
       <c r="B44" t="n">
-        <v>79689</v>
+        <v>79688</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5205,21 +5205,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5229,13 +5229,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520232</v>
+        <v>520278</v>
       </c>
       <c r="R44" t="n">
-        <v>6967691</v>
+        <v>6967715</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5301,10 +5301,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121478200</v>
+        <v>121481678</v>
       </c>
       <c r="B45" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5317,21 +5317,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5341,13 +5341,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519995</v>
+        <v>520220</v>
       </c>
       <c r="R45" t="n">
-        <v>6967827</v>
+        <v>6967688</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5413,7 +5413,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121481087</v>
+        <v>121481685</v>
       </c>
       <c r="B46" t="n">
         <v>79688</v>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520115</v>
+        <v>520238</v>
       </c>
       <c r="R46" t="n">
-        <v>6967640</v>
+        <v>6967692</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121481479</v>
+        <v>121477474</v>
       </c>
       <c r="B22" t="n">
-        <v>79688</v>
+        <v>90713</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520117</v>
+        <v>519997</v>
       </c>
       <c r="R22" t="n">
-        <v>6967650</v>
+        <v>6967748</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121477474</v>
+        <v>121481479</v>
       </c>
       <c r="B23" t="n">
-        <v>90713</v>
+        <v>79688</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2863,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519997</v>
+        <v>520117</v>
       </c>
       <c r="R23" t="n">
-        <v>6967748</v>
+        <v>6967650</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121477474</v>
+        <v>121481758</v>
       </c>
       <c r="B22" t="n">
-        <v>90713</v>
+        <v>79689</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519997</v>
+        <v>520254</v>
       </c>
       <c r="R22" t="n">
-        <v>6967748</v>
+        <v>6967738</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121481479</v>
+        <v>121481699</v>
       </c>
       <c r="B23" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520117</v>
+        <v>520237</v>
       </c>
       <c r="R23" t="n">
-        <v>6967650</v>
+        <v>6967698</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2959,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121480924</v>
+        <v>121481087</v>
       </c>
       <c r="B24" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520122</v>
+        <v>520115</v>
       </c>
       <c r="R24" t="n">
-        <v>6967652</v>
+        <v>6967640</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3071,10 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121476235</v>
+        <v>121481595</v>
       </c>
       <c r="B25" t="n">
-        <v>90713</v>
+        <v>79689</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3087,21 +3087,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3111,13 +3111,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519974</v>
+        <v>520162</v>
       </c>
       <c r="R25" t="n">
-        <v>6967729</v>
+        <v>6967675</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,10 +3183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121481087</v>
+        <v>121478601</v>
       </c>
       <c r="B26" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,17 +3219,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+          <t>Långmyrberget, Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520115</v>
+        <v>519990</v>
       </c>
       <c r="R26" t="n">
-        <v>6967640</v>
+        <v>6967852</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3295,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121481563</v>
+        <v>121481619</v>
       </c>
       <c r="B27" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3335,13 +3335,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520152</v>
+        <v>520190</v>
       </c>
       <c r="R27" t="n">
-        <v>6967652</v>
+        <v>6967698</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3407,10 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121481677</v>
+        <v>121481678</v>
       </c>
       <c r="B28" t="n">
-        <v>79688</v>
+        <v>79690</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520234</v>
+        <v>520220</v>
       </c>
       <c r="R28" t="n">
-        <v>6967703</v>
+        <v>6967688</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3519,10 +3519,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121481332</v>
+        <v>121481691</v>
       </c>
       <c r="B29" t="n">
-        <v>79688</v>
+        <v>79690</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3535,21 +3535,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520108</v>
+        <v>520232</v>
       </c>
       <c r="R29" t="n">
-        <v>6967640</v>
+        <v>6967691</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3631,10 +3631,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121481637</v>
+        <v>121481479</v>
       </c>
       <c r="B30" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3671,13 +3671,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520215</v>
+        <v>520117</v>
       </c>
       <c r="R30" t="n">
-        <v>6967683</v>
+        <v>6967650</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3746,7 +3746,7 @@
         <v>121481704</v>
       </c>
       <c r="B31" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3855,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121481742</v>
+        <v>121477474</v>
       </c>
       <c r="B32" t="n">
-        <v>79688</v>
+        <v>90719</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3871,21 +3871,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520275</v>
+        <v>519997</v>
       </c>
       <c r="R32" t="n">
-        <v>6967730</v>
+        <v>6967748</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,10 +3967,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121479853</v>
+        <v>121481563</v>
       </c>
       <c r="B33" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4007,13 +4007,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520028</v>
+        <v>520152</v>
       </c>
       <c r="R33" t="n">
-        <v>6967759</v>
+        <v>6967652</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4079,10 +4079,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121478200</v>
+        <v>121481732</v>
       </c>
       <c r="B34" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519995</v>
+        <v>520278</v>
       </c>
       <c r="R34" t="n">
-        <v>6967827</v>
+        <v>6967715</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4191,10 +4191,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121478601</v>
+        <v>121481677</v>
       </c>
       <c r="B35" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4227,17 +4227,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långmyrberget, Långmyrberget, Jmt</t>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519990</v>
+        <v>520234</v>
       </c>
       <c r="R35" t="n">
-        <v>6967852</v>
+        <v>6967703</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,10 +4303,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121481758</v>
+        <v>121476235</v>
       </c>
       <c r="B36" t="n">
-        <v>79688</v>
+        <v>90719</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4319,21 +4319,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4343,10 +4343,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520254</v>
+        <v>519974</v>
       </c>
       <c r="R36" t="n">
-        <v>6967738</v>
+        <v>6967729</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4415,10 +4415,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121481738</v>
+        <v>121481742</v>
       </c>
       <c r="B37" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520268</v>
+        <v>520275</v>
       </c>
       <c r="R37" t="n">
-        <v>6967719</v>
+        <v>6967730</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121481572</v>
+        <v>121481685</v>
       </c>
       <c r="B38" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520158</v>
+        <v>520238</v>
       </c>
       <c r="R38" t="n">
-        <v>6967663</v>
+        <v>6967692</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,7 +4639,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121481558</v>
+        <v>121481738</v>
       </c>
       <c r="B39" t="n">
         <v>79689</v>
@@ -4655,21 +4655,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4679,10 +4679,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520195</v>
+        <v>520268</v>
       </c>
       <c r="R39" t="n">
-        <v>6967685</v>
+        <v>6967719</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4712,9 +4712,19 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,7 +4751,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121481691</v>
+        <v>121481572</v>
       </c>
       <c r="B40" t="n">
         <v>79689</v>
@@ -4757,21 +4767,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4781,10 +4791,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>520232</v>
+        <v>520158</v>
       </c>
       <c r="R40" t="n">
-        <v>6967691</v>
+        <v>6967663</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4816,7 +4826,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4826,7 +4836,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,10 +4863,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121481699</v>
+        <v>121480924</v>
       </c>
       <c r="B41" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4893,10 +4903,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520237</v>
+        <v>520122</v>
       </c>
       <c r="R41" t="n">
-        <v>6967698</v>
+        <v>6967652</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4928,7 +4938,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4938,7 +4948,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4965,10 +4975,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121481619</v>
+        <v>121481558</v>
       </c>
       <c r="B42" t="n">
-        <v>79688</v>
+        <v>79690</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4981,21 +4991,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5005,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520190</v>
+        <v>520195</v>
       </c>
       <c r="R42" t="n">
-        <v>6967698</v>
+        <v>6967685</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5038,19 +5048,9 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5077,10 +5077,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121481595</v>
+        <v>121481332</v>
       </c>
       <c r="B43" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5117,13 +5117,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520162</v>
+        <v>520108</v>
       </c>
       <c r="R43" t="n">
-        <v>6967675</v>
+        <v>6967640</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5189,10 +5189,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121481732</v>
+        <v>121481637</v>
       </c>
       <c r="B44" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520278</v>
+        <v>520215</v>
       </c>
       <c r="R44" t="n">
-        <v>6967715</v>
+        <v>6967683</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5301,7 +5301,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121481678</v>
+        <v>121478200</v>
       </c>
       <c r="B45" t="n">
         <v>79689</v>
@@ -5317,21 +5317,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5341,13 +5341,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520220</v>
+        <v>519995</v>
       </c>
       <c r="R45" t="n">
-        <v>6967688</v>
+        <v>6967827</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5413,10 +5413,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121481685</v>
+        <v>121479853</v>
       </c>
       <c r="B46" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520238</v>
+        <v>520028</v>
       </c>
       <c r="R46" t="n">
-        <v>6967692</v>
+        <v>6967759</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -4191,10 +4191,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121481677</v>
+        <v>121476235</v>
       </c>
       <c r="B35" t="n">
-        <v>79689</v>
+        <v>90719</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4207,21 +4207,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520234</v>
+        <v>519974</v>
       </c>
       <c r="R35" t="n">
-        <v>6967703</v>
+        <v>6967729</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,10 +4303,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121476235</v>
+        <v>121481677</v>
       </c>
       <c r="B36" t="n">
-        <v>90719</v>
+        <v>79689</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4319,21 +4319,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4343,10 +4343,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519974</v>
+        <v>520234</v>
       </c>
       <c r="R36" t="n">
-        <v>6967729</v>
+        <v>6967703</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4863,10 +4863,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121480924</v>
+        <v>121481558</v>
       </c>
       <c r="B41" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4879,21 +4879,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4903,10 +4903,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520122</v>
+        <v>520195</v>
       </c>
       <c r="R41" t="n">
-        <v>6967652</v>
+        <v>6967685</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4936,19 +4936,9 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>12:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4975,10 +4965,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121481558</v>
+        <v>121480924</v>
       </c>
       <c r="B42" t="n">
-        <v>79690</v>
+        <v>79689</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4991,21 +4981,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5015,10 +5005,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520195</v>
+        <v>520122</v>
       </c>
       <c r="R42" t="n">
-        <v>6967685</v>
+        <v>6967652</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5048,9 +5038,19 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121481758</v>
+        <v>121481678</v>
       </c>
       <c r="B22" t="n">
-        <v>79689</v>
+        <v>79691</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520254</v>
+        <v>520220</v>
       </c>
       <c r="R22" t="n">
-        <v>6967738</v>
+        <v>6967688</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121481699</v>
+        <v>121481637</v>
       </c>
       <c r="B23" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520237</v>
+        <v>520215</v>
       </c>
       <c r="R23" t="n">
-        <v>6967698</v>
+        <v>6967683</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2959,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121481087</v>
+        <v>121481619</v>
       </c>
       <c r="B24" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520115</v>
+        <v>520190</v>
       </c>
       <c r="R24" t="n">
-        <v>6967640</v>
+        <v>6967698</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3071,10 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121481595</v>
+        <v>121477474</v>
       </c>
       <c r="B25" t="n">
-        <v>79689</v>
+        <v>90720</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3087,21 +3087,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520162</v>
+        <v>519997</v>
       </c>
       <c r="R25" t="n">
-        <v>6967675</v>
+        <v>6967748</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,10 +3183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121478601</v>
+        <v>121476235</v>
       </c>
       <c r="B26" t="n">
-        <v>79689</v>
+        <v>90720</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3199,37 +3199,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långmyrberget, Långmyrberget, Jmt</t>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519990</v>
+        <v>519974</v>
       </c>
       <c r="R26" t="n">
-        <v>6967852</v>
+        <v>6967729</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3295,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121481619</v>
+        <v>121481479</v>
       </c>
       <c r="B27" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520190</v>
+        <v>520117</v>
       </c>
       <c r="R27" t="n">
-        <v>6967698</v>
+        <v>6967650</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3407,7 +3407,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121481678</v>
+        <v>121480924</v>
       </c>
       <c r="B28" t="n">
         <v>79690</v>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520220</v>
+        <v>520122</v>
       </c>
       <c r="R28" t="n">
-        <v>6967688</v>
+        <v>6967652</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3519,7 +3519,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121481691</v>
+        <v>121481563</v>
       </c>
       <c r="B29" t="n">
         <v>79690</v>
@@ -3535,21 +3535,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520232</v>
+        <v>520152</v>
       </c>
       <c r="R29" t="n">
-        <v>6967691</v>
+        <v>6967652</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3631,10 +3631,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121481479</v>
+        <v>121481738</v>
       </c>
       <c r="B30" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520117</v>
+        <v>520268</v>
       </c>
       <c r="R30" t="n">
-        <v>6967650</v>
+        <v>6967719</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3743,10 +3743,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121481704</v>
+        <v>121481572</v>
       </c>
       <c r="B31" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520220</v>
+        <v>520158</v>
       </c>
       <c r="R31" t="n">
-        <v>6967703</v>
+        <v>6967663</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121477474</v>
+        <v>121481677</v>
       </c>
       <c r="B32" t="n">
-        <v>90719</v>
+        <v>79690</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3871,21 +3871,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519997</v>
+        <v>520234</v>
       </c>
       <c r="R32" t="n">
-        <v>6967748</v>
+        <v>6967703</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,10 +3967,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121481563</v>
+        <v>121481087</v>
       </c>
       <c r="B33" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4007,13 +4007,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520152</v>
+        <v>520115</v>
       </c>
       <c r="R33" t="n">
-        <v>6967652</v>
+        <v>6967640</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4082,7 +4082,7 @@
         <v>121481732</v>
       </c>
       <c r="B34" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4191,10 +4191,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121476235</v>
+        <v>121481685</v>
       </c>
       <c r="B35" t="n">
-        <v>90719</v>
+        <v>79690</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4207,21 +4207,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519974</v>
+        <v>520238</v>
       </c>
       <c r="R35" t="n">
-        <v>6967729</v>
+        <v>6967692</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,10 +4303,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121481677</v>
+        <v>121478200</v>
       </c>
       <c r="B36" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4343,13 +4343,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520234</v>
+        <v>519995</v>
       </c>
       <c r="R36" t="n">
-        <v>6967703</v>
+        <v>6967827</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4415,10 +4415,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121481742</v>
+        <v>121479853</v>
       </c>
       <c r="B37" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520275</v>
+        <v>520028</v>
       </c>
       <c r="R37" t="n">
-        <v>6967730</v>
+        <v>6967759</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121481685</v>
+        <v>121481742</v>
       </c>
       <c r="B38" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520238</v>
+        <v>520275</v>
       </c>
       <c r="R38" t="n">
-        <v>6967692</v>
+        <v>6967730</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,10 +4639,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121481738</v>
+        <v>121481704</v>
       </c>
       <c r="B39" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4679,10 +4679,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520268</v>
+        <v>520220</v>
       </c>
       <c r="R39" t="n">
-        <v>6967719</v>
+        <v>6967703</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4751,10 +4751,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121481572</v>
+        <v>121481758</v>
       </c>
       <c r="B40" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4791,10 +4791,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>520158</v>
+        <v>520254</v>
       </c>
       <c r="R40" t="n">
-        <v>6967663</v>
+        <v>6967738</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4863,7 +4863,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121481558</v>
+        <v>121481332</v>
       </c>
       <c r="B41" t="n">
         <v>79690</v>
@@ -4879,21 +4879,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4903,10 +4903,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520195</v>
+        <v>520108</v>
       </c>
       <c r="R41" t="n">
-        <v>6967685</v>
+        <v>6967640</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4936,9 +4936,19 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4965,10 +4975,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121480924</v>
+        <v>121481558</v>
       </c>
       <c r="B42" t="n">
-        <v>79689</v>
+        <v>79691</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4981,21 +4991,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5005,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520122</v>
+        <v>520195</v>
       </c>
       <c r="R42" t="n">
-        <v>6967652</v>
+        <v>6967685</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5038,19 +5048,9 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:48</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5077,10 +5077,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121481332</v>
+        <v>121481691</v>
       </c>
       <c r="B43" t="n">
-        <v>79689</v>
+        <v>79691</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5093,21 +5093,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520108</v>
+        <v>520232</v>
       </c>
       <c r="R43" t="n">
-        <v>6967640</v>
+        <v>6967691</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5189,10 +5189,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121481637</v>
+        <v>121481595</v>
       </c>
       <c r="B44" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520215</v>
+        <v>520162</v>
       </c>
       <c r="R44" t="n">
-        <v>6967683</v>
+        <v>6967675</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5301,10 +5301,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121478200</v>
+        <v>121478601</v>
       </c>
       <c r="B45" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5337,14 +5337,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+          <t>Långmyrberget, Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519995</v>
+        <v>519990</v>
       </c>
       <c r="R45" t="n">
-        <v>6967827</v>
+        <v>6967852</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5413,10 +5413,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121479853</v>
+        <v>121481699</v>
       </c>
       <c r="B46" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520028</v>
+        <v>520237</v>
       </c>
       <c r="R46" t="n">
-        <v>6967759</v>
+        <v>6967698</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121481678</v>
+        <v>121481677</v>
       </c>
       <c r="B22" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520220</v>
+        <v>520234</v>
       </c>
       <c r="R22" t="n">
-        <v>6967688</v>
+        <v>6967703</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3071,10 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121477474</v>
+        <v>121481563</v>
       </c>
       <c r="B25" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3087,21 +3087,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519997</v>
+        <v>520152</v>
       </c>
       <c r="R25" t="n">
-        <v>6967748</v>
+        <v>6967652</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,10 +3183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121476235</v>
+        <v>121478200</v>
       </c>
       <c r="B26" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3199,21 +3199,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3223,13 +3223,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519974</v>
+        <v>519995</v>
       </c>
       <c r="R26" t="n">
-        <v>6967729</v>
+        <v>6967827</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3295,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121481479</v>
+        <v>121481691</v>
       </c>
       <c r="B27" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3311,21 +3311,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520117</v>
+        <v>520232</v>
       </c>
       <c r="R27" t="n">
-        <v>6967650</v>
+        <v>6967691</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3407,7 +3407,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121480924</v>
+        <v>121481738</v>
       </c>
       <c r="B28" t="n">
         <v>79690</v>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520122</v>
+        <v>520268</v>
       </c>
       <c r="R28" t="n">
-        <v>6967652</v>
+        <v>6967719</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3519,7 +3519,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121481563</v>
+        <v>121481595</v>
       </c>
       <c r="B29" t="n">
         <v>79690</v>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520152</v>
+        <v>520162</v>
       </c>
       <c r="R29" t="n">
-        <v>6967652</v>
+        <v>6967675</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121481738</v>
+        <v>121481332</v>
       </c>
       <c r="B30" t="n">
         <v>79690</v>
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520268</v>
+        <v>520108</v>
       </c>
       <c r="R30" t="n">
-        <v>6967719</v>
+        <v>6967640</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3743,7 +3743,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121481572</v>
+        <v>121481699</v>
       </c>
       <c r="B31" t="n">
         <v>79690</v>
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520158</v>
+        <v>520237</v>
       </c>
       <c r="R31" t="n">
-        <v>6967663</v>
+        <v>6967698</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,7 +3855,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121481677</v>
+        <v>121480924</v>
       </c>
       <c r="B32" t="n">
         <v>79690</v>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520234</v>
+        <v>520122</v>
       </c>
       <c r="R32" t="n">
-        <v>6967703</v>
+        <v>6967652</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,7 +3967,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121481087</v>
+        <v>121481685</v>
       </c>
       <c r="B33" t="n">
         <v>79690</v>
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520115</v>
+        <v>520238</v>
       </c>
       <c r="R33" t="n">
-        <v>6967640</v>
+        <v>6967692</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4079,10 +4079,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121481732</v>
+        <v>121477474</v>
       </c>
       <c r="B34" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4095,21 +4095,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520278</v>
+        <v>519997</v>
       </c>
       <c r="R34" t="n">
-        <v>6967715</v>
+        <v>6967748</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4191,10 +4191,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121481685</v>
+        <v>121481678</v>
       </c>
       <c r="B35" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4207,21 +4207,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520238</v>
+        <v>520220</v>
       </c>
       <c r="R35" t="n">
-        <v>6967692</v>
+        <v>6967688</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,7 +4303,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121478200</v>
+        <v>121478601</v>
       </c>
       <c r="B36" t="n">
         <v>79690</v>
@@ -4339,14 +4339,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+          <t>Långmyrberget, Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519995</v>
+        <v>519990</v>
       </c>
       <c r="R36" t="n">
-        <v>6967827</v>
+        <v>6967852</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4527,7 +4527,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121481742</v>
+        <v>121481704</v>
       </c>
       <c r="B38" t="n">
         <v>79690</v>
@@ -4567,10 +4567,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520275</v>
+        <v>520220</v>
       </c>
       <c r="R38" t="n">
-        <v>6967730</v>
+        <v>6967703</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,7 +4639,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121481704</v>
+        <v>121481087</v>
       </c>
       <c r="B39" t="n">
         <v>79690</v>
@@ -4679,10 +4679,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520220</v>
+        <v>520115</v>
       </c>
       <c r="R39" t="n">
-        <v>6967703</v>
+        <v>6967640</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4863,7 +4863,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121481332</v>
+        <v>121481479</v>
       </c>
       <c r="B41" t="n">
         <v>79690</v>
@@ -4903,10 +4903,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520108</v>
+        <v>520117</v>
       </c>
       <c r="R41" t="n">
-        <v>6967640</v>
+        <v>6967650</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4975,10 +4975,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121481558</v>
+        <v>121476235</v>
       </c>
       <c r="B42" t="n">
-        <v>79691</v>
+        <v>90720</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4991,21 +4991,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520195</v>
+        <v>519974</v>
       </c>
       <c r="R42" t="n">
-        <v>6967685</v>
+        <v>6967729</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5048,9 +5048,19 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5077,10 +5087,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121481691</v>
+        <v>121481742</v>
       </c>
       <c r="B43" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5093,21 +5103,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5117,10 +5127,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520232</v>
+        <v>520275</v>
       </c>
       <c r="R43" t="n">
-        <v>6967691</v>
+        <v>6967730</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5152,7 +5162,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5162,7 +5172,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5189,7 +5199,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121481595</v>
+        <v>121481732</v>
       </c>
       <c r="B44" t="n">
         <v>79690</v>
@@ -5229,10 +5239,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520162</v>
+        <v>520278</v>
       </c>
       <c r="R44" t="n">
-        <v>6967675</v>
+        <v>6967715</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5264,7 +5274,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5274,7 +5284,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5301,10 +5311,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121478601</v>
+        <v>121481558</v>
       </c>
       <c r="B45" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5317,37 +5327,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Långmyrberget, Långmyrberget, Jmt</t>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519990</v>
+        <v>520195</v>
       </c>
       <c r="R45" t="n">
-        <v>6967852</v>
+        <v>6967685</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5374,19 +5384,9 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5413,7 +5413,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121481699</v>
+        <v>121481572</v>
       </c>
       <c r="B46" t="n">
         <v>79690</v>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520237</v>
+        <v>520158</v>
       </c>
       <c r="R46" t="n">
-        <v>6967698</v>
+        <v>6967663</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -2735,7 +2735,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121481677</v>
+        <v>121481699</v>
       </c>
       <c r="B22" t="n">
         <v>79690</v>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520234</v>
+        <v>520237</v>
       </c>
       <c r="R22" t="n">
-        <v>6967703</v>
+        <v>6967698</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121481637</v>
+        <v>121476235</v>
       </c>
       <c r="B23" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2863,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520215</v>
+        <v>519974</v>
       </c>
       <c r="R23" t="n">
-        <v>6967683</v>
+        <v>6967729</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2959,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121481619</v>
+        <v>121481691</v>
       </c>
       <c r="B24" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2975,21 +2975,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520190</v>
+        <v>520232</v>
       </c>
       <c r="R24" t="n">
-        <v>6967698</v>
+        <v>6967691</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3071,7 +3071,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121481563</v>
+        <v>121481619</v>
       </c>
       <c r="B25" t="n">
         <v>79690</v>
@@ -3111,13 +3111,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520152</v>
+        <v>520190</v>
       </c>
       <c r="R25" t="n">
-        <v>6967652</v>
+        <v>6967698</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,7 +3183,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121478200</v>
+        <v>121481742</v>
       </c>
       <c r="B26" t="n">
         <v>79690</v>
@@ -3223,13 +3223,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519995</v>
+        <v>520275</v>
       </c>
       <c r="R26" t="n">
-        <v>6967827</v>
+        <v>6967730</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3295,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121481691</v>
+        <v>121479853</v>
       </c>
       <c r="B27" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3311,21 +3311,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520232</v>
+        <v>520028</v>
       </c>
       <c r="R27" t="n">
-        <v>6967691</v>
+        <v>6967759</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3407,7 +3407,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121481738</v>
+        <v>121481677</v>
       </c>
       <c r="B28" t="n">
         <v>79690</v>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520268</v>
+        <v>520234</v>
       </c>
       <c r="R28" t="n">
-        <v>6967719</v>
+        <v>6967703</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3519,7 +3519,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121481595</v>
+        <v>121481479</v>
       </c>
       <c r="B29" t="n">
         <v>79690</v>
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520162</v>
+        <v>520117</v>
       </c>
       <c r="R29" t="n">
-        <v>6967675</v>
+        <v>6967650</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121481332</v>
+        <v>121478200</v>
       </c>
       <c r="B30" t="n">
         <v>79690</v>
@@ -3671,13 +3671,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520108</v>
+        <v>519995</v>
       </c>
       <c r="R30" t="n">
-        <v>6967640</v>
+        <v>6967827</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3743,10 +3743,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121481699</v>
+        <v>121477474</v>
       </c>
       <c r="B31" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3759,21 +3759,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3783,13 +3783,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520237</v>
+        <v>519997</v>
       </c>
       <c r="R31" t="n">
-        <v>6967698</v>
+        <v>6967748</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,7 +3855,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121480924</v>
+        <v>121481758</v>
       </c>
       <c r="B32" t="n">
         <v>79690</v>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520122</v>
+        <v>520254</v>
       </c>
       <c r="R32" t="n">
-        <v>6967652</v>
+        <v>6967738</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,7 +3967,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121481685</v>
+        <v>121481704</v>
       </c>
       <c r="B33" t="n">
         <v>79690</v>
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520238</v>
+        <v>520220</v>
       </c>
       <c r="R33" t="n">
-        <v>6967692</v>
+        <v>6967703</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4079,10 +4079,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121477474</v>
+        <v>121481595</v>
       </c>
       <c r="B34" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4095,21 +4095,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519997</v>
+        <v>520162</v>
       </c>
       <c r="R34" t="n">
-        <v>6967748</v>
+        <v>6967675</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4191,7 +4191,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121481678</v>
+        <v>121481558</v>
       </c>
       <c r="B35" t="n">
         <v>79691</v>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520220</v>
+        <v>520195</v>
       </c>
       <c r="R35" t="n">
-        <v>6967688</v>
+        <v>6967685</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4264,19 +4264,9 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4415,7 +4405,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121479853</v>
+        <v>121481685</v>
       </c>
       <c r="B37" t="n">
         <v>79690</v>
@@ -4455,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520028</v>
+        <v>520238</v>
       </c>
       <c r="R37" t="n">
-        <v>6967759</v>
+        <v>6967692</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4480,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4490,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,7 +4517,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121481704</v>
+        <v>121481738</v>
       </c>
       <c r="B38" t="n">
         <v>79690</v>
@@ -4567,10 +4557,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520220</v>
+        <v>520268</v>
       </c>
       <c r="R38" t="n">
-        <v>6967703</v>
+        <v>6967719</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4602,7 +4592,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4612,7 +4602,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,7 +4629,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121481087</v>
+        <v>121480924</v>
       </c>
       <c r="B39" t="n">
         <v>79690</v>
@@ -4679,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520115</v>
+        <v>520122</v>
       </c>
       <c r="R39" t="n">
-        <v>6967640</v>
+        <v>6967652</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4714,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4724,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4751,7 +4741,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121481758</v>
+        <v>121481563</v>
       </c>
       <c r="B40" t="n">
         <v>79690</v>
@@ -4791,13 +4781,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>520254</v>
+        <v>520152</v>
       </c>
       <c r="R40" t="n">
-        <v>6967738</v>
+        <v>6967652</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4826,7 +4816,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4836,7 +4826,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4863,7 +4853,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121481479</v>
+        <v>121481572</v>
       </c>
       <c r="B41" t="n">
         <v>79690</v>
@@ -4903,10 +4893,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520117</v>
+        <v>520158</v>
       </c>
       <c r="R41" t="n">
-        <v>6967650</v>
+        <v>6967663</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4938,7 +4928,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4948,7 +4938,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4975,10 +4965,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121476235</v>
+        <v>121481332</v>
       </c>
       <c r="B42" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4991,21 +4981,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5015,10 +5005,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519974</v>
+        <v>520108</v>
       </c>
       <c r="R42" t="n">
-        <v>6967729</v>
+        <v>6967640</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5050,7 +5040,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5060,7 +5050,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5087,10 +5077,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121481742</v>
+        <v>121481678</v>
       </c>
       <c r="B43" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5103,21 +5093,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5127,10 +5117,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520275</v>
+        <v>520220</v>
       </c>
       <c r="R43" t="n">
-        <v>6967730</v>
+        <v>6967688</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5162,7 +5152,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5172,7 +5162,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5311,10 +5301,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121481558</v>
+        <v>121481087</v>
       </c>
       <c r="B45" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5327,21 +5317,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5351,10 +5341,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520195</v>
+        <v>520115</v>
       </c>
       <c r="R45" t="n">
-        <v>6967685</v>
+        <v>6967640</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5384,9 +5374,19 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5413,7 +5413,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121481572</v>
+        <v>121481637</v>
       </c>
       <c r="B46" t="n">
         <v>79690</v>
@@ -5453,13 +5453,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520158</v>
+        <v>520215</v>
       </c>
       <c r="R46" t="n">
-        <v>6967663</v>
+        <v>6967683</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121481699</v>
+        <v>121481558</v>
       </c>
       <c r="B22" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520237</v>
+        <v>520195</v>
       </c>
       <c r="R22" t="n">
-        <v>6967698</v>
+        <v>6967685</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2808,19 +2808,9 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121476235</v>
+        <v>121481677</v>
       </c>
       <c r="B23" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2863,21 +2853,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2887,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519974</v>
+        <v>520234</v>
       </c>
       <c r="R23" t="n">
-        <v>6967729</v>
+        <v>6967703</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2922,7 +2912,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2932,7 +2922,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2959,10 +2949,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121481691</v>
+        <v>121481572</v>
       </c>
       <c r="B24" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2975,21 +2965,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2999,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520232</v>
+        <v>520158</v>
       </c>
       <c r="R24" t="n">
-        <v>6967691</v>
+        <v>6967663</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3034,7 +3024,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3044,7 +3034,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3071,7 +3061,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121481619</v>
+        <v>121478200</v>
       </c>
       <c r="B25" t="n">
         <v>79690</v>
@@ -3111,13 +3101,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520190</v>
+        <v>519995</v>
       </c>
       <c r="R25" t="n">
-        <v>6967698</v>
+        <v>6967827</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3146,7 +3136,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3156,7 +3146,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,7 +3173,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121481742</v>
+        <v>121481685</v>
       </c>
       <c r="B26" t="n">
         <v>79690</v>
@@ -3223,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520275</v>
+        <v>520238</v>
       </c>
       <c r="R26" t="n">
-        <v>6967730</v>
+        <v>6967692</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3258,7 +3248,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3268,7 +3258,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3295,7 +3285,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121479853</v>
+        <v>121481479</v>
       </c>
       <c r="B27" t="n">
         <v>79690</v>
@@ -3335,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520028</v>
+        <v>520117</v>
       </c>
       <c r="R27" t="n">
-        <v>6967759</v>
+        <v>6967650</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,7 +3360,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3380,7 +3370,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3407,7 +3397,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121481677</v>
+        <v>121481742</v>
       </c>
       <c r="B28" t="n">
         <v>79690</v>
@@ -3447,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520234</v>
+        <v>520275</v>
       </c>
       <c r="R28" t="n">
-        <v>6967703</v>
+        <v>6967730</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3482,7 +3472,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3492,7 +3482,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3519,7 +3509,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121481479</v>
+        <v>121481738</v>
       </c>
       <c r="B29" t="n">
         <v>79690</v>
@@ -3559,10 +3549,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520117</v>
+        <v>520268</v>
       </c>
       <c r="R29" t="n">
-        <v>6967650</v>
+        <v>6967719</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3594,7 +3584,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3604,7 +3594,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3631,10 +3621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121478200</v>
+        <v>121481691</v>
       </c>
       <c r="B30" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3647,21 +3637,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3671,13 +3661,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519995</v>
+        <v>520232</v>
       </c>
       <c r="R30" t="n">
-        <v>6967827</v>
+        <v>6967691</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3706,7 +3696,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3716,7 +3706,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3743,10 +3733,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121477474</v>
+        <v>121478601</v>
       </c>
       <c r="B31" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3759,34 +3749,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+          <t>Långmyrberget, Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519997</v>
+        <v>519990</v>
       </c>
       <c r="R31" t="n">
-        <v>6967748</v>
+        <v>6967852</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3818,7 +3808,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3828,7 +3818,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,7 +3845,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121481758</v>
+        <v>121481732</v>
       </c>
       <c r="B32" t="n">
         <v>79690</v>
@@ -3895,13 +3885,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520254</v>
+        <v>520278</v>
       </c>
       <c r="R32" t="n">
-        <v>6967738</v>
+        <v>6967715</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3930,7 +3920,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3940,7 +3930,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,7 +3957,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121481704</v>
+        <v>121481087</v>
       </c>
       <c r="B33" t="n">
         <v>79690</v>
@@ -4007,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520220</v>
+        <v>520115</v>
       </c>
       <c r="R33" t="n">
-        <v>6967703</v>
+        <v>6967640</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4042,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4052,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4079,7 +4069,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121481595</v>
+        <v>121481563</v>
       </c>
       <c r="B34" t="n">
         <v>79690</v>
@@ -4119,10 +4109,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520162</v>
+        <v>520152</v>
       </c>
       <c r="R34" t="n">
-        <v>6967675</v>
+        <v>6967652</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4154,7 +4144,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4164,7 +4154,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4191,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121481558</v>
+        <v>121481758</v>
       </c>
       <c r="B35" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4207,21 +4197,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4221,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520195</v>
+        <v>520254</v>
       </c>
       <c r="R35" t="n">
-        <v>6967685</v>
+        <v>6967738</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4264,9 +4254,19 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4293,10 +4293,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121478601</v>
+        <v>121481678</v>
       </c>
       <c r="B36" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4309,37 +4309,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långmyrberget, Långmyrberget, Jmt</t>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519990</v>
+        <v>520220</v>
       </c>
       <c r="R36" t="n">
-        <v>6967852</v>
+        <v>6967688</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4405,7 +4405,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121481685</v>
+        <v>121480924</v>
       </c>
       <c r="B37" t="n">
         <v>79690</v>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520238</v>
+        <v>520122</v>
       </c>
       <c r="R37" t="n">
-        <v>6967692</v>
+        <v>6967652</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,7 +4517,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121481738</v>
+        <v>121479853</v>
       </c>
       <c r="B38" t="n">
         <v>79690</v>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520268</v>
+        <v>520028</v>
       </c>
       <c r="R38" t="n">
-        <v>6967719</v>
+        <v>6967759</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4629,7 +4629,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121480924</v>
+        <v>121481704</v>
       </c>
       <c r="B39" t="n">
         <v>79690</v>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520122</v>
+        <v>520220</v>
       </c>
       <c r="R39" t="n">
-        <v>6967652</v>
+        <v>6967703</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,7 +4741,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121481563</v>
+        <v>121481332</v>
       </c>
       <c r="B40" t="n">
         <v>79690</v>
@@ -4781,13 +4781,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>520152</v>
+        <v>520108</v>
       </c>
       <c r="R40" t="n">
-        <v>6967652</v>
+        <v>6967640</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,7 +4853,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121481572</v>
+        <v>121481637</v>
       </c>
       <c r="B41" t="n">
         <v>79690</v>
@@ -4893,13 +4893,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520158</v>
+        <v>520215</v>
       </c>
       <c r="R41" t="n">
-        <v>6967663</v>
+        <v>6967683</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4965,10 +4965,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121481332</v>
+        <v>121476235</v>
       </c>
       <c r="B42" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4981,21 +4981,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520108</v>
+        <v>519974</v>
       </c>
       <c r="R42" t="n">
-        <v>6967640</v>
+        <v>6967729</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5077,10 +5077,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121481678</v>
+        <v>121477474</v>
       </c>
       <c r="B43" t="n">
-        <v>79691</v>
+        <v>90720</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5093,21 +5093,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5117,13 +5117,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520220</v>
+        <v>519997</v>
       </c>
       <c r="R43" t="n">
-        <v>6967688</v>
+        <v>6967748</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5189,7 +5189,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121481732</v>
+        <v>121481699</v>
       </c>
       <c r="B44" t="n">
         <v>79690</v>
@@ -5229,13 +5229,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520278</v>
+        <v>520237</v>
       </c>
       <c r="R44" t="n">
-        <v>6967715</v>
+        <v>6967698</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5301,7 +5301,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121481087</v>
+        <v>121481595</v>
       </c>
       <c r="B45" t="n">
         <v>79690</v>
@@ -5341,13 +5341,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520115</v>
+        <v>520162</v>
       </c>
       <c r="R45" t="n">
-        <v>6967640</v>
+        <v>6967675</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5413,7 +5413,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121481637</v>
+        <v>121481619</v>
       </c>
       <c r="B46" t="n">
         <v>79690</v>
@@ -5453,13 +5453,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520215</v>
+        <v>520190</v>
       </c>
       <c r="R46" t="n">
-        <v>6967683</v>
+        <v>6967698</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121481558</v>
+        <v>121478200</v>
       </c>
       <c r="B22" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520195</v>
+        <v>519995</v>
       </c>
       <c r="R22" t="n">
-        <v>6967685</v>
+        <v>6967827</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2808,9 +2808,19 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3061,10 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121478200</v>
+        <v>121481558</v>
       </c>
       <c r="B25" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3077,21 +3087,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3101,13 +3111,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519995</v>
+        <v>520195</v>
       </c>
       <c r="R25" t="n">
-        <v>6967827</v>
+        <v>6967685</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3134,19 +3144,9 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121478200</v>
+        <v>121481558</v>
       </c>
       <c r="B22" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519995</v>
+        <v>520195</v>
       </c>
       <c r="R22" t="n">
-        <v>6967827</v>
+        <v>6967685</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2808,19 +2808,9 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3071,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121481558</v>
+        <v>121478200</v>
       </c>
       <c r="B25" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3087,21 +3077,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3111,13 +3101,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520195</v>
+        <v>519995</v>
       </c>
       <c r="R25" t="n">
-        <v>6967685</v>
+        <v>6967827</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3144,9 +3134,19 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121481558</v>
+        <v>121481738</v>
       </c>
       <c r="B22" t="n">
-        <v>79691</v>
+        <v>79697</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520195</v>
+        <v>520268</v>
       </c>
       <c r="R22" t="n">
-        <v>6967685</v>
+        <v>6967719</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2808,9 +2808,19 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2837,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121481677</v>
+        <v>121481691</v>
       </c>
       <c r="B23" t="n">
-        <v>79690</v>
+        <v>79698</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520234</v>
+        <v>520232</v>
       </c>
       <c r="R23" t="n">
-        <v>6967703</v>
+        <v>6967691</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2912,7 +2922,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2922,7 +2932,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2949,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121481572</v>
+        <v>121481479</v>
       </c>
       <c r="B24" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2989,10 +2999,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520158</v>
+        <v>520117</v>
       </c>
       <c r="R24" t="n">
-        <v>6967663</v>
+        <v>6967650</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3024,7 +3034,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3034,7 +3044,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,10 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121478200</v>
+        <v>121477474</v>
       </c>
       <c r="B25" t="n">
-        <v>79690</v>
+        <v>90728</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3077,21 +3087,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3101,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519995</v>
+        <v>519997</v>
       </c>
       <c r="R25" t="n">
-        <v>6967827</v>
+        <v>6967748</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3136,7 +3146,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3146,7 +3156,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3173,10 +3183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121481685</v>
+        <v>121481637</v>
       </c>
       <c r="B26" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3213,13 +3223,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520238</v>
+        <v>520215</v>
       </c>
       <c r="R26" t="n">
-        <v>6967692</v>
+        <v>6967683</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3248,7 +3258,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3258,7 +3268,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3285,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121481479</v>
+        <v>121480924</v>
       </c>
       <c r="B27" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3325,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520117</v>
+        <v>520122</v>
       </c>
       <c r="R27" t="n">
-        <v>6967650</v>
+        <v>6967652</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3360,7 +3370,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3370,7 +3380,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3397,10 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121481742</v>
+        <v>121481758</v>
       </c>
       <c r="B28" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3437,10 +3447,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520275</v>
+        <v>520254</v>
       </c>
       <c r="R28" t="n">
-        <v>6967730</v>
+        <v>6967738</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,7 +3482,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3482,7 +3492,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3509,10 +3519,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121481738</v>
+        <v>121476235</v>
       </c>
       <c r="B29" t="n">
-        <v>79690</v>
+        <v>90728</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3525,21 +3535,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3549,10 +3559,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520268</v>
+        <v>519974</v>
       </c>
       <c r="R29" t="n">
-        <v>6967719</v>
+        <v>6967729</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3584,7 +3594,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3594,7 +3604,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3621,10 +3631,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121481691</v>
+        <v>121481678</v>
       </c>
       <c r="B30" t="n">
-        <v>79691</v>
+        <v>79698</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3661,10 +3671,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520232</v>
+        <v>520220</v>
       </c>
       <c r="R30" t="n">
-        <v>6967691</v>
+        <v>6967688</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3696,7 +3706,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3706,7 +3716,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3733,10 +3743,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121478601</v>
+        <v>121481572</v>
       </c>
       <c r="B31" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3769,17 +3779,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långmyrberget, Långmyrberget, Jmt</t>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519990</v>
+        <v>520158</v>
       </c>
       <c r="R31" t="n">
-        <v>6967852</v>
+        <v>6967663</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3808,7 +3818,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3818,7 +3828,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3848,7 +3858,7 @@
         <v>121481732</v>
       </c>
       <c r="B32" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3957,10 +3967,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121481087</v>
+        <v>121481677</v>
       </c>
       <c r="B33" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3997,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520115</v>
+        <v>520234</v>
       </c>
       <c r="R33" t="n">
-        <v>6967640</v>
+        <v>6967703</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4032,7 +4042,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4052,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,10 +4079,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121481563</v>
+        <v>121478200</v>
       </c>
       <c r="B34" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4109,10 +4119,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520152</v>
+        <v>519995</v>
       </c>
       <c r="R34" t="n">
-        <v>6967652</v>
+        <v>6967827</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4144,7 +4154,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4154,7 +4164,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4181,10 +4191,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121481758</v>
+        <v>121478601</v>
       </c>
       <c r="B35" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4217,17 +4227,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+          <t>Långmyrberget, Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520254</v>
+        <v>519990</v>
       </c>
       <c r="R35" t="n">
-        <v>6967738</v>
+        <v>6967852</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4256,7 +4266,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4266,7 +4276,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4293,10 +4303,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121481678</v>
+        <v>121481685</v>
       </c>
       <c r="B36" t="n">
-        <v>79691</v>
+        <v>79697</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4309,21 +4319,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4333,10 +4343,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520220</v>
+        <v>520238</v>
       </c>
       <c r="R36" t="n">
-        <v>6967688</v>
+        <v>6967692</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4368,7 +4378,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4378,7 +4388,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4405,10 +4415,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121480924</v>
+        <v>121481704</v>
       </c>
       <c r="B37" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4445,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520122</v>
+        <v>520220</v>
       </c>
       <c r="R37" t="n">
-        <v>6967652</v>
+        <v>6967703</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4520,7 +4530,7 @@
         <v>121479853</v>
       </c>
       <c r="B38" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4629,10 +4639,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121481704</v>
+        <v>121481332</v>
       </c>
       <c r="B39" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4669,10 +4679,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520220</v>
+        <v>520108</v>
       </c>
       <c r="R39" t="n">
-        <v>6967703</v>
+        <v>6967640</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4714,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4714,7 +4724,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,10 +4751,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121481332</v>
+        <v>121481619</v>
       </c>
       <c r="B40" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4781,10 +4791,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>520108</v>
+        <v>520190</v>
       </c>
       <c r="R40" t="n">
-        <v>6967640</v>
+        <v>6967698</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4816,7 +4826,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4826,7 +4836,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,10 +4863,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121481637</v>
+        <v>121481087</v>
       </c>
       <c r="B41" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4893,13 +4903,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520215</v>
+        <v>520115</v>
       </c>
       <c r="R41" t="n">
-        <v>6967683</v>
+        <v>6967640</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4928,7 +4938,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4938,7 +4948,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4965,10 +4975,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121476235</v>
+        <v>121481558</v>
       </c>
       <c r="B42" t="n">
-        <v>90720</v>
+        <v>79698</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4981,21 +4991,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5005,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519974</v>
+        <v>520195</v>
       </c>
       <c r="R42" t="n">
-        <v>6967729</v>
+        <v>6967685</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5038,19 +5048,9 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5077,10 +5077,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121477474</v>
+        <v>121481595</v>
       </c>
       <c r="B43" t="n">
-        <v>90720</v>
+        <v>79697</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5093,21 +5093,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519997</v>
+        <v>520162</v>
       </c>
       <c r="R43" t="n">
-        <v>6967748</v>
+        <v>6967675</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5192,7 +5192,7 @@
         <v>121481699</v>
       </c>
       <c r="B44" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5301,10 +5301,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121481595</v>
+        <v>121481563</v>
       </c>
       <c r="B45" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520162</v>
+        <v>520152</v>
       </c>
       <c r="R45" t="n">
-        <v>6967675</v>
+        <v>6967652</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5413,10 +5413,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121481619</v>
+        <v>121481742</v>
       </c>
       <c r="B46" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520190</v>
+        <v>520275</v>
       </c>
       <c r="R46" t="n">
-        <v>6967698</v>
+        <v>6967730</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -4863,10 +4863,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121481087</v>
+        <v>121481558</v>
       </c>
       <c r="B41" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4879,21 +4879,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4903,10 +4903,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520115</v>
+        <v>520195</v>
       </c>
       <c r="R41" t="n">
-        <v>6967640</v>
+        <v>6967685</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4936,19 +4936,9 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>12:49</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>12:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4975,10 +4965,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121481558</v>
+        <v>121481595</v>
       </c>
       <c r="B42" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4991,21 +4981,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5015,13 +5005,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520195</v>
+        <v>520162</v>
       </c>
       <c r="R42" t="n">
-        <v>6967685</v>
+        <v>6967675</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5048,9 +5038,19 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5077,7 +5077,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121481595</v>
+        <v>121481087</v>
       </c>
       <c r="B43" t="n">
         <v>79697</v>
@@ -5117,13 +5117,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520162</v>
+        <v>520115</v>
       </c>
       <c r="R43" t="n">
-        <v>6967675</v>
+        <v>6967640</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121481479</v>
+        <v>121477474</v>
       </c>
       <c r="B22" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520117</v>
+        <v>519997</v>
       </c>
       <c r="R22" t="n">
-        <v>6967650</v>
+        <v>6967748</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,7 +2847,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121481738</v>
+        <v>121481685</v>
       </c>
       <c r="B23" t="n">
         <v>79697</v>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520268</v>
+        <v>520238</v>
       </c>
       <c r="R23" t="n">
-        <v>6967719</v>
+        <v>6967692</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2959,7 +2959,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121480924</v>
+        <v>121481087</v>
       </c>
       <c r="B24" t="n">
         <v>79697</v>
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520122</v>
+        <v>520115</v>
       </c>
       <c r="R24" t="n">
-        <v>6967652</v>
+        <v>6967640</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3071,7 +3071,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121481087</v>
+        <v>121478200</v>
       </c>
       <c r="B25" t="n">
         <v>79697</v>
@@ -3111,13 +3111,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520115</v>
+        <v>519995</v>
       </c>
       <c r="R25" t="n">
-        <v>6967640</v>
+        <v>6967827</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,7 +3183,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121481619</v>
+        <v>121481637</v>
       </c>
       <c r="B26" t="n">
         <v>79697</v>
@@ -3223,13 +3223,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520190</v>
+        <v>520215</v>
       </c>
       <c r="R26" t="n">
-        <v>6967698</v>
+        <v>6967683</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3295,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121481572</v>
+        <v>121481678</v>
       </c>
       <c r="B27" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3311,21 +3311,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520158</v>
+        <v>520220</v>
       </c>
       <c r="R27" t="n">
-        <v>6967663</v>
+        <v>6967688</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3407,10 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121477474</v>
+        <v>121481558</v>
       </c>
       <c r="B28" t="n">
-        <v>90728</v>
+        <v>79698</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519997</v>
+        <v>520195</v>
       </c>
       <c r="R28" t="n">
-        <v>6967748</v>
+        <v>6967685</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3480,19 +3480,9 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3519,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121481685</v>
+        <v>121476235</v>
       </c>
       <c r="B29" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3535,21 +3525,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3559,10 +3549,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520238</v>
+        <v>519974</v>
       </c>
       <c r="R29" t="n">
-        <v>6967692</v>
+        <v>6967729</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3594,7 +3584,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3604,7 +3594,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3631,10 +3621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121481678</v>
+        <v>121481619</v>
       </c>
       <c r="B30" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3647,21 +3637,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3671,10 +3661,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520220</v>
+        <v>520190</v>
       </c>
       <c r="R30" t="n">
-        <v>6967688</v>
+        <v>6967698</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3706,7 +3696,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3716,7 +3706,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3743,7 +3733,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121481758</v>
+        <v>121481677</v>
       </c>
       <c r="B31" t="n">
         <v>79697</v>
@@ -3783,10 +3773,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520254</v>
+        <v>520234</v>
       </c>
       <c r="R31" t="n">
-        <v>6967738</v>
+        <v>6967703</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3818,7 +3808,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3828,7 +3818,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,7 +3845,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121478200</v>
+        <v>121478601</v>
       </c>
       <c r="B32" t="n">
         <v>79697</v>
@@ -3891,14 +3881,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+          <t>Långmyrberget, Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519995</v>
+        <v>519990</v>
       </c>
       <c r="R32" t="n">
-        <v>6967827</v>
+        <v>6967852</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3930,7 +3920,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3940,7 +3930,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,7 +3957,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121478601</v>
+        <v>121480924</v>
       </c>
       <c r="B33" t="n">
         <v>79697</v>
@@ -4003,17 +3993,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långmyrberget, Långmyrberget, Jmt</t>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519990</v>
+        <v>520122</v>
       </c>
       <c r="R33" t="n">
-        <v>6967852</v>
+        <v>6967652</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4042,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4052,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4079,7 +4069,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121481637</v>
+        <v>121479853</v>
       </c>
       <c r="B34" t="n">
         <v>79697</v>
@@ -4119,13 +4109,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520215</v>
+        <v>520028</v>
       </c>
       <c r="R34" t="n">
-        <v>6967683</v>
+        <v>6967759</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4154,7 +4144,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4164,7 +4154,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4191,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121481558</v>
+        <v>121481699</v>
       </c>
       <c r="B35" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4207,21 +4197,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4221,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520195</v>
+        <v>520237</v>
       </c>
       <c r="R35" t="n">
-        <v>6967685</v>
+        <v>6967698</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4264,9 +4254,19 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4293,7 +4293,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121481699</v>
+        <v>121481479</v>
       </c>
       <c r="B36" t="n">
         <v>79697</v>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520237</v>
+        <v>520117</v>
       </c>
       <c r="R36" t="n">
-        <v>6967698</v>
+        <v>6967650</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4405,10 +4405,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121481563</v>
+        <v>121481691</v>
       </c>
       <c r="B37" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4421,21 +4421,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4445,13 +4445,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520152</v>
+        <v>520232</v>
       </c>
       <c r="R37" t="n">
-        <v>6967652</v>
+        <v>6967691</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,7 +4517,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121481742</v>
+        <v>121481732</v>
       </c>
       <c r="B38" t="n">
         <v>79697</v>
@@ -4557,13 +4557,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520275</v>
+        <v>520278</v>
       </c>
       <c r="R38" t="n">
-        <v>6967730</v>
+        <v>6967715</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4629,10 +4629,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121481691</v>
+        <v>121481758</v>
       </c>
       <c r="B39" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520232</v>
+        <v>520254</v>
       </c>
       <c r="R39" t="n">
-        <v>6967691</v>
+        <v>6967738</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,7 +4741,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121481332</v>
+        <v>121481563</v>
       </c>
       <c r="B40" t="n">
         <v>79697</v>
@@ -4781,13 +4781,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>520108</v>
+        <v>520152</v>
       </c>
       <c r="R40" t="n">
-        <v>6967640</v>
+        <v>6967652</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,7 +4853,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121481704</v>
+        <v>121481738</v>
       </c>
       <c r="B41" t="n">
         <v>79697</v>
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520220</v>
+        <v>520268</v>
       </c>
       <c r="R41" t="n">
-        <v>6967703</v>
+        <v>6967719</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4965,10 +4965,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121476235</v>
+        <v>121481704</v>
       </c>
       <c r="B42" t="n">
-        <v>90728</v>
+        <v>79697</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4981,21 +4981,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519974</v>
+        <v>520220</v>
       </c>
       <c r="R42" t="n">
-        <v>6967729</v>
+        <v>6967703</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5077,7 +5077,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121481732</v>
+        <v>121481742</v>
       </c>
       <c r="B43" t="n">
         <v>79697</v>
@@ -5117,13 +5117,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520278</v>
+        <v>520275</v>
       </c>
       <c r="R43" t="n">
-        <v>6967715</v>
+        <v>6967730</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5189,7 +5189,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121481677</v>
+        <v>121481595</v>
       </c>
       <c r="B44" t="n">
         <v>79697</v>
@@ -5229,13 +5229,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520234</v>
+        <v>520162</v>
       </c>
       <c r="R44" t="n">
-        <v>6967703</v>
+        <v>6967675</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5301,7 +5301,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121479853</v>
+        <v>121481332</v>
       </c>
       <c r="B45" t="n">
         <v>79697</v>
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520028</v>
+        <v>520108</v>
       </c>
       <c r="R45" t="n">
-        <v>6967759</v>
+        <v>6967640</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5413,7 +5413,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121481595</v>
+        <v>121481572</v>
       </c>
       <c r="B46" t="n">
         <v>79697</v>
@@ -5453,13 +5453,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520162</v>
+        <v>520158</v>
       </c>
       <c r="R46" t="n">
-        <v>6967675</v>
+        <v>6967663</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -4181,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121481699</v>
+        <v>121481691</v>
       </c>
       <c r="B35" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4197,21 +4197,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4221,10 +4221,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520237</v>
+        <v>520232</v>
       </c>
       <c r="R35" t="n">
-        <v>6967698</v>
+        <v>6967691</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4293,7 +4293,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121481479</v>
+        <v>121481699</v>
       </c>
       <c r="B36" t="n">
         <v>79697</v>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520117</v>
+        <v>520237</v>
       </c>
       <c r="R36" t="n">
-        <v>6967650</v>
+        <v>6967698</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4405,10 +4405,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121481691</v>
+        <v>121481479</v>
       </c>
       <c r="B37" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4421,21 +4421,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520232</v>
+        <v>520117</v>
       </c>
       <c r="R37" t="n">
-        <v>6967691</v>
+        <v>6967650</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121477474</v>
+        <v>121481637</v>
       </c>
       <c r="B22" t="n">
-        <v>90728</v>
+        <v>79697</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519997</v>
+        <v>520215</v>
       </c>
       <c r="R22" t="n">
-        <v>6967748</v>
+        <v>6967683</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,7 +2847,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121481685</v>
+        <v>121478601</v>
       </c>
       <c r="B23" t="n">
         <v>79697</v>
@@ -2883,17 +2883,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+          <t>Långmyrberget, Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520238</v>
+        <v>519990</v>
       </c>
       <c r="R23" t="n">
-        <v>6967692</v>
+        <v>6967852</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2959,7 +2959,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121481087</v>
+        <v>121481742</v>
       </c>
       <c r="B24" t="n">
         <v>79697</v>
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520115</v>
+        <v>520275</v>
       </c>
       <c r="R24" t="n">
-        <v>6967640</v>
+        <v>6967730</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3071,7 +3071,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121478200</v>
+        <v>121481677</v>
       </c>
       <c r="B25" t="n">
         <v>79697</v>
@@ -3111,13 +3111,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519995</v>
+        <v>520234</v>
       </c>
       <c r="R25" t="n">
-        <v>6967827</v>
+        <v>6967703</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,10 +3183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121481637</v>
+        <v>121476235</v>
       </c>
       <c r="B26" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3199,21 +3199,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3223,13 +3223,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520215</v>
+        <v>519974</v>
       </c>
       <c r="R26" t="n">
-        <v>6967683</v>
+        <v>6967729</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3295,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121481678</v>
+        <v>121481332</v>
       </c>
       <c r="B27" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3311,21 +3311,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520220</v>
+        <v>520108</v>
       </c>
       <c r="R27" t="n">
-        <v>6967688</v>
+        <v>6967640</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3407,10 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121481558</v>
+        <v>121481479</v>
       </c>
       <c r="B28" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520195</v>
+        <v>520117</v>
       </c>
       <c r="R28" t="n">
-        <v>6967685</v>
+        <v>6967650</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3480,9 +3480,19 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3509,10 +3519,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121476235</v>
+        <v>121481563</v>
       </c>
       <c r="B29" t="n">
-        <v>90728</v>
+        <v>79697</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3525,21 +3535,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3549,13 +3559,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519974</v>
+        <v>520152</v>
       </c>
       <c r="R29" t="n">
-        <v>6967729</v>
+        <v>6967652</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3584,7 +3594,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3594,7 +3604,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3621,7 +3631,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121481619</v>
+        <v>121481732</v>
       </c>
       <c r="B30" t="n">
         <v>79697</v>
@@ -3661,13 +3671,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520190</v>
+        <v>520278</v>
       </c>
       <c r="R30" t="n">
-        <v>6967698</v>
+        <v>6967715</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3696,7 +3706,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3706,7 +3716,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3733,7 +3743,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121481677</v>
+        <v>121481758</v>
       </c>
       <c r="B31" t="n">
         <v>79697</v>
@@ -3773,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520234</v>
+        <v>520254</v>
       </c>
       <c r="R31" t="n">
-        <v>6967703</v>
+        <v>6967738</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3808,7 +3818,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3818,7 +3828,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3845,7 +3855,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121478601</v>
+        <v>121481738</v>
       </c>
       <c r="B32" t="n">
         <v>79697</v>
@@ -3881,17 +3891,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långmyrberget, Långmyrberget, Jmt</t>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519990</v>
+        <v>520268</v>
       </c>
       <c r="R32" t="n">
-        <v>6967852</v>
+        <v>6967719</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3920,7 +3930,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3930,7 +3940,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3957,7 +3967,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121480924</v>
+        <v>121481572</v>
       </c>
       <c r="B33" t="n">
         <v>79697</v>
@@ -3997,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520122</v>
+        <v>520158</v>
       </c>
       <c r="R33" t="n">
-        <v>6967652</v>
+        <v>6967663</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4032,7 +4042,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4042,7 +4052,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,10 +4079,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121479853</v>
+        <v>121481678</v>
       </c>
       <c r="B34" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4085,21 +4095,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4109,10 +4119,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520028</v>
+        <v>520220</v>
       </c>
       <c r="R34" t="n">
-        <v>6967759</v>
+        <v>6967688</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4144,7 +4154,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4154,7 +4164,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4181,10 +4191,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121481691</v>
+        <v>121481087</v>
       </c>
       <c r="B35" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4197,21 +4207,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4221,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520232</v>
+        <v>520115</v>
       </c>
       <c r="R35" t="n">
-        <v>6967691</v>
+        <v>6967640</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4256,7 +4266,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4266,7 +4276,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4293,7 +4303,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121481699</v>
+        <v>121481704</v>
       </c>
       <c r="B36" t="n">
         <v>79697</v>
@@ -4333,10 +4343,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520237</v>
+        <v>520220</v>
       </c>
       <c r="R36" t="n">
-        <v>6967698</v>
+        <v>6967703</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4368,7 +4378,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4378,7 +4388,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4405,7 +4415,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121481479</v>
+        <v>121481685</v>
       </c>
       <c r="B37" t="n">
         <v>79697</v>
@@ -4445,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520117</v>
+        <v>520238</v>
       </c>
       <c r="R37" t="n">
-        <v>6967650</v>
+        <v>6967692</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,7 +4527,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121481732</v>
+        <v>121480924</v>
       </c>
       <c r="B38" t="n">
         <v>79697</v>
@@ -4557,13 +4567,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520278</v>
+        <v>520122</v>
       </c>
       <c r="R38" t="n">
-        <v>6967715</v>
+        <v>6967652</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4592,7 +4602,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4602,7 +4612,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4629,7 +4639,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121481758</v>
+        <v>121481699</v>
       </c>
       <c r="B39" t="n">
         <v>79697</v>
@@ -4669,10 +4679,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520254</v>
+        <v>520237</v>
       </c>
       <c r="R39" t="n">
-        <v>6967738</v>
+        <v>6967698</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4714,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4714,7 +4724,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,10 +4751,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121481563</v>
+        <v>121481691</v>
       </c>
       <c r="B40" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4757,21 +4767,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4781,13 +4791,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>520152</v>
+        <v>520232</v>
       </c>
       <c r="R40" t="n">
-        <v>6967652</v>
+        <v>6967691</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4816,7 +4826,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4826,7 +4836,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,7 +4863,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121481738</v>
+        <v>121478200</v>
       </c>
       <c r="B41" t="n">
         <v>79697</v>
@@ -4893,13 +4903,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520268</v>
+        <v>519995</v>
       </c>
       <c r="R41" t="n">
-        <v>6967719</v>
+        <v>6967827</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4928,7 +4938,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4938,7 +4948,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4965,7 +4975,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121481704</v>
+        <v>121481595</v>
       </c>
       <c r="B42" t="n">
         <v>79697</v>
@@ -5005,13 +5015,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520220</v>
+        <v>520162</v>
       </c>
       <c r="R42" t="n">
-        <v>6967703</v>
+        <v>6967675</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5040,7 +5050,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5050,7 +5060,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5077,10 +5087,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121481742</v>
+        <v>121477474</v>
       </c>
       <c r="B43" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5093,21 +5103,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5117,13 +5127,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520275</v>
+        <v>519997</v>
       </c>
       <c r="R43" t="n">
-        <v>6967730</v>
+        <v>6967748</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5152,7 +5162,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5162,7 +5172,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5189,10 +5199,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121481595</v>
+        <v>121481558</v>
       </c>
       <c r="B44" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5205,21 +5215,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5229,13 +5239,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520162</v>
+        <v>520195</v>
       </c>
       <c r="R44" t="n">
-        <v>6967675</v>
+        <v>6967685</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5262,19 +5272,9 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5301,7 +5301,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121481332</v>
+        <v>121479853</v>
       </c>
       <c r="B45" t="n">
         <v>79697</v>
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520108</v>
+        <v>520028</v>
       </c>
       <c r="R45" t="n">
-        <v>6967640</v>
+        <v>6967759</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5413,7 +5413,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121481572</v>
+        <v>121481619</v>
       </c>
       <c r="B46" t="n">
         <v>79697</v>
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520158</v>
+        <v>520190</v>
       </c>
       <c r="R46" t="n">
-        <v>6967663</v>
+        <v>6967698</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5523,6 +5523,399 @@
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>125708287</v>
+      </c>
+      <c r="B47" t="n">
+        <v>100413</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Långmyrtjärnen, Långmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>520039</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6967764</v>
+      </c>
+      <c r="S47" t="n">
+        <v>20</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125708069</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Långmyrtjärnen, Långmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>519998</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6967847</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>125708240</v>
+      </c>
+      <c r="B49" t="n">
+        <v>100506</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Långmyrtjärnen, Långmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>520042</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6967770</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125708219</v>
+      </c>
+      <c r="B50" t="n">
+        <v>101410</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Långmyrtjärnen, Långmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>520045</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6967756</v>
+      </c>
+      <c r="S50" t="n">
+        <v>20</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -5525,32 +5525,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125708287</v>
+        <v>125708069</v>
       </c>
       <c r="B47" t="n">
-        <v>100413</v>
+        <v>80070</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5560,13 +5560,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520039</v>
+        <v>519998</v>
       </c>
       <c r="R47" t="n">
-        <v>6967764</v>
+        <v>6967847</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5596,6 +5596,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5622,32 +5627,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125708069</v>
+        <v>125708287</v>
       </c>
       <c r="B48" t="n">
-        <v>80070</v>
+        <v>100413</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5657,13 +5662,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519998</v>
+        <v>520039</v>
       </c>
       <c r="R48" t="n">
-        <v>6967847</v>
+        <v>6967764</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5693,11 +5698,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -5525,32 +5525,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125708069</v>
+        <v>125708287</v>
       </c>
       <c r="B47" t="n">
-        <v>80070</v>
+        <v>100420</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5560,13 +5560,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519998</v>
+        <v>520039</v>
       </c>
       <c r="R47" t="n">
-        <v>6967847</v>
+        <v>6967764</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5596,11 +5596,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5627,32 +5622,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125708287</v>
+        <v>125708069</v>
       </c>
       <c r="B48" t="n">
-        <v>100413</v>
+        <v>80070</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5662,13 +5657,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>520039</v>
+        <v>519998</v>
       </c>
       <c r="R48" t="n">
-        <v>6967764</v>
+        <v>6967847</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5698,6 +5693,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5727,7 +5727,7 @@
         <v>125708240</v>
       </c>
       <c r="B49" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>125708219</v>
       </c>
       <c r="B50" t="n">
-        <v>101410</v>
+        <v>101417</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -5525,32 +5525,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125708287</v>
+        <v>125708069</v>
       </c>
       <c r="B47" t="n">
-        <v>100420</v>
+        <v>80070</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5560,13 +5560,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520039</v>
+        <v>519998</v>
       </c>
       <c r="R47" t="n">
-        <v>6967764</v>
+        <v>6967847</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5596,6 +5596,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5622,32 +5627,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125708069</v>
+        <v>125708287</v>
       </c>
       <c r="B48" t="n">
-        <v>80070</v>
+        <v>100420</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5657,13 +5662,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519998</v>
+        <v>520039</v>
       </c>
       <c r="R48" t="n">
-        <v>6967847</v>
+        <v>6967764</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5693,11 +5698,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -5528,7 +5528,7 @@
         <v>125708069</v>
       </c>
       <c r="B47" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>125708287</v>
       </c>
       <c r="B48" t="n">
-        <v>100420</v>
+        <v>100423</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>125708240</v>
       </c>
       <c r="B49" t="n">
-        <v>100513</v>
+        <v>100516</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>125708219</v>
       </c>
       <c r="B50" t="n">
-        <v>101417</v>
+        <v>101420</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -5528,7 +5528,7 @@
         <v>125708069</v>
       </c>
       <c r="B47" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>125708287</v>
       </c>
       <c r="B48" t="n">
-        <v>100423</v>
+        <v>100427</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>125708240</v>
       </c>
       <c r="B49" t="n">
-        <v>100516</v>
+        <v>100520</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>125708219</v>
       </c>
       <c r="B50" t="n">
-        <v>101420</v>
+        <v>101424</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -5630,7 +5630,7 @@
         <v>125708287</v>
       </c>
       <c r="B48" t="n">
-        <v>100427</v>
+        <v>100428</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>125708240</v>
       </c>
       <c r="B49" t="n">
-        <v>100520</v>
+        <v>100521</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>125708219</v>
       </c>
       <c r="B50" t="n">
-        <v>101424</v>
+        <v>101425</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -5525,32 +5525,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125708069</v>
+        <v>125708287</v>
       </c>
       <c r="B47" t="n">
-        <v>80075</v>
+        <v>100428</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5560,13 +5560,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519998</v>
+        <v>520039</v>
       </c>
       <c r="R47" t="n">
-        <v>6967847</v>
+        <v>6967764</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5596,11 +5596,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5627,32 +5622,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125708287</v>
+        <v>125708069</v>
       </c>
       <c r="B48" t="n">
-        <v>100428</v>
+        <v>80075</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5662,13 +5657,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>520039</v>
+        <v>519998</v>
       </c>
       <c r="R48" t="n">
-        <v>6967764</v>
+        <v>6967847</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5698,6 +5693,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -5525,32 +5525,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125708287</v>
+        <v>125708069</v>
       </c>
       <c r="B47" t="n">
-        <v>100428</v>
+        <v>80076</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5560,13 +5560,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520039</v>
+        <v>519998</v>
       </c>
       <c r="R47" t="n">
-        <v>6967764</v>
+        <v>6967847</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5596,6 +5596,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5622,32 +5627,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125708069</v>
+        <v>125708287</v>
       </c>
       <c r="B48" t="n">
-        <v>80075</v>
+        <v>100430</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5657,13 +5662,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519998</v>
+        <v>520039</v>
       </c>
       <c r="R48" t="n">
-        <v>6967847</v>
+        <v>6967764</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5693,11 +5698,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5727,7 +5727,7 @@
         <v>125708240</v>
       </c>
       <c r="B49" t="n">
-        <v>100521</v>
+        <v>100523</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>125708219</v>
       </c>
       <c r="B50" t="n">
-        <v>101425</v>
+        <v>101427</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -5525,32 +5525,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125708069</v>
+        <v>125708287</v>
       </c>
       <c r="B47" t="n">
-        <v>80076</v>
+        <v>100432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5560,13 +5560,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519998</v>
+        <v>520039</v>
       </c>
       <c r="R47" t="n">
-        <v>6967847</v>
+        <v>6967764</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5596,11 +5596,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5627,32 +5622,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125708287</v>
+        <v>125708069</v>
       </c>
       <c r="B48" t="n">
-        <v>100430</v>
+        <v>80076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5662,13 +5657,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>520039</v>
+        <v>519998</v>
       </c>
       <c r="R48" t="n">
-        <v>6967764</v>
+        <v>6967847</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5698,6 +5693,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5727,7 +5727,7 @@
         <v>125708240</v>
       </c>
       <c r="B49" t="n">
-        <v>100523</v>
+        <v>100525</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>125708219</v>
       </c>
       <c r="B50" t="n">
-        <v>101427</v>
+        <v>101429</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -5525,32 +5525,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125708287</v>
+        <v>125708069</v>
       </c>
       <c r="B47" t="n">
-        <v>100432</v>
+        <v>80076</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5560,13 +5560,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520039</v>
+        <v>519998</v>
       </c>
       <c r="R47" t="n">
-        <v>6967764</v>
+        <v>6967847</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5596,6 +5596,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5622,32 +5627,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125708069</v>
+        <v>125708287</v>
       </c>
       <c r="B48" t="n">
-        <v>80076</v>
+        <v>100434</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5657,13 +5662,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519998</v>
+        <v>520039</v>
       </c>
       <c r="R48" t="n">
-        <v>6967847</v>
+        <v>6967764</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5693,11 +5698,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5727,7 +5727,7 @@
         <v>125708240</v>
       </c>
       <c r="B49" t="n">
-        <v>100525</v>
+        <v>100527</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>125708219</v>
       </c>
       <c r="B50" t="n">
-        <v>101429</v>
+        <v>101431</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -5528,7 +5528,7 @@
         <v>125708069</v>
       </c>
       <c r="B47" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>125708287</v>
       </c>
       <c r="B48" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>125708240</v>
       </c>
       <c r="B49" t="n">
-        <v>100527</v>
+        <v>100531</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>125708219</v>
       </c>
       <c r="B50" t="n">
-        <v>101431</v>
+        <v>101435</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 60326-2023 artfynd.xlsx
+++ b/artfynd/A 60326-2023 artfynd.xlsx
@@ -5630,7 +5630,7 @@
         <v>125708287</v>
       </c>
       <c r="B48" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>125708240</v>
       </c>
       <c r="B49" t="n">
-        <v>100531</v>
+        <v>100534</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>125708219</v>
       </c>
       <c r="B50" t="n">
-        <v>101435</v>
+        <v>101438</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
